--- a/saipe_2000_2010.xlsx
+++ b/saipe_2000_2010.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1117"/>
+  <dimension ref="A1:E1024"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B2">
@@ -405,7 +405,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B3">
@@ -426,7 +426,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B4">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B5">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B6">
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B7">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B8">
@@ -531,7 +531,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B9">
@@ -552,7 +552,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B10">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B11">
@@ -594,7 +594,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B12">
@@ -615,7 +615,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B13">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B14">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B15">
@@ -678,7 +678,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B16">
@@ -699,7 +699,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B17">
@@ -720,7 +720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B18">
@@ -741,7 +741,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B19">
@@ -762,7 +762,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B20">
@@ -783,7 +783,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B21">
@@ -804,7 +804,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B22">
@@ -825,7 +825,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B23">
@@ -846,7 +846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B24">
@@ -867,7 +867,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B25">
@@ -888,7 +888,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B26">
@@ -909,7 +909,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B27">
@@ -930,7 +930,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B28">
@@ -951,7 +951,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B29">
@@ -972,7 +972,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B30">
@@ -993,7 +993,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B31">
@@ -1014,7 +1014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B32">
@@ -1035,7 +1035,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B33">
@@ -1056,7 +1056,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B34">
@@ -1077,7 +1077,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B35">
@@ -1098,7 +1098,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B36">
@@ -1119,7 +1119,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B37">
@@ -1140,7 +1140,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B38">
@@ -1161,7 +1161,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B39">
@@ -1182,7 +1182,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B40">
@@ -1203,7 +1203,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B41">
@@ -1224,7 +1224,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B42">
@@ -1245,7 +1245,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B43">
@@ -1266,7 +1266,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B44">
@@ -1287,7 +1287,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B45">
@@ -1308,7 +1308,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B46">
@@ -1329,7 +1329,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B47">
@@ -1350,7 +1350,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B48">
@@ -1371,7 +1371,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B49">
@@ -1392,7 +1392,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B50">
@@ -1413,7 +1413,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B51">
@@ -1434,7 +1434,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B52">
@@ -2337,7 +2337,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B95">
@@ -2358,7 +2358,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B96">
@@ -2379,7 +2379,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B97">
@@ -2400,7 +2400,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B98">
@@ -2421,7 +2421,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B99">
@@ -2442,7 +2442,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B100">
@@ -2463,7 +2463,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B101">
@@ -2484,7 +2484,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B102">
@@ -2505,7 +2505,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B103">
@@ -2526,7 +2526,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B104">
@@ -2547,7 +2547,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B105">
@@ -2568,7 +2568,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B106">
@@ -2589,7 +2589,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B107">
@@ -2610,7 +2610,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B108">
@@ -2631,7 +2631,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B109">
@@ -2652,7 +2652,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B110">
@@ -2673,7 +2673,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B111">
@@ -2694,7 +2694,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B112">
@@ -2715,7 +2715,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B113">
@@ -2736,7 +2736,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B114">
@@ -2757,7 +2757,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B115">
@@ -2778,7 +2778,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B116">
@@ -2799,7 +2799,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B117">
@@ -2820,7 +2820,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B118">
@@ -2841,7 +2841,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B119">
@@ -2862,7 +2862,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B120">
@@ -2883,7 +2883,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B121">
@@ -2904,7 +2904,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B122">
@@ -2925,7 +2925,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B123">
@@ -2946,7 +2946,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B124">
@@ -2967,7 +2967,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B125">
@@ -2988,7 +2988,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B126">
@@ -3009,7 +3009,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B127">
@@ -3030,7 +3030,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B128">
@@ -3051,7 +3051,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B129">
@@ -3072,7 +3072,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B130">
@@ -3093,7 +3093,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B131">
@@ -3114,7 +3114,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B132">
@@ -3135,7 +3135,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B133">
@@ -3156,7 +3156,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B134">
@@ -3177,7 +3177,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B135">
@@ -3198,7 +3198,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B136">
@@ -3219,7 +3219,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B137">
@@ -3240,7 +3240,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B138">
@@ -3261,7 +3261,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B139">
@@ -3282,7 +3282,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B140">
@@ -3303,7 +3303,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B141">
@@ -3324,7 +3324,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B142">
@@ -3345,7 +3345,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B143">
@@ -3366,7 +3366,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B144">
@@ -3387,7 +3387,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B145">
@@ -4290,7 +4290,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B188">
@@ -4311,7 +4311,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B189">
@@ -4332,7 +4332,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B190">
@@ -4353,7 +4353,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B191">
@@ -4374,7 +4374,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B192">
@@ -4395,7 +4395,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B193">
@@ -4416,7 +4416,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B194">
@@ -4437,7 +4437,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B195">
@@ -4458,7 +4458,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B196">
@@ -4479,7 +4479,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B197">
@@ -4500,7 +4500,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B198">
@@ -4521,7 +4521,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B199">
@@ -4542,7 +4542,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B200">
@@ -4563,7 +4563,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B201">
@@ -4584,7 +4584,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B202">
@@ -4605,7 +4605,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B203">
@@ -4626,7 +4626,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B204">
@@ -4647,7 +4647,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B205">
@@ -4668,7 +4668,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B206">
@@ -4689,7 +4689,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B207">
@@ -4710,7 +4710,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B208">
@@ -4731,7 +4731,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B209">
@@ -4752,7 +4752,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B210">
@@ -4773,7 +4773,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B211">
@@ -4794,7 +4794,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B212">
@@ -4815,7 +4815,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B213">
@@ -4836,7 +4836,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B214">
@@ -4857,7 +4857,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B215">
@@ -4878,7 +4878,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B216">
@@ -4899,7 +4899,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B217">
@@ -4920,7 +4920,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B218">
@@ -4941,7 +4941,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B219">
@@ -4962,7 +4962,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B220">
@@ -4983,7 +4983,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B221">
@@ -5004,7 +5004,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B222">
@@ -5025,7 +5025,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B223">
@@ -5046,7 +5046,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B224">
@@ -5067,7 +5067,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B225">
@@ -5088,7 +5088,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B226">
@@ -5109,7 +5109,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B227">
@@ -5130,7 +5130,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B228">
@@ -5151,7 +5151,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B229">
@@ -5172,7 +5172,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B230">
@@ -5193,7 +5193,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B231">
@@ -5214,7 +5214,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B232">
@@ -5235,7 +5235,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B233">
@@ -5256,7 +5256,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B234">
@@ -5277,7 +5277,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B235">
@@ -5298,7 +5298,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B236">
@@ -5319,7 +5319,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B237">
@@ -5340,7 +5340,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B238">
@@ -6243,7 +6243,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B281">
@@ -6264,7 +6264,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B282">
@@ -6285,7 +6285,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B283">
@@ -6306,7 +6306,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B284">
@@ -6327,7 +6327,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B285">
@@ -6348,7 +6348,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B286">
@@ -6369,7 +6369,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B287">
@@ -6390,7 +6390,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B288">
@@ -6411,7 +6411,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B289">
@@ -6432,7 +6432,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B290">
@@ -6453,7 +6453,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B291">
@@ -6474,7 +6474,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B292">
@@ -6495,7 +6495,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B293">
@@ -6516,7 +6516,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B294">
@@ -6537,7 +6537,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B295">
@@ -6558,7 +6558,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B296">
@@ -6579,7 +6579,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B297">
@@ -6600,7 +6600,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B298">
@@ -6621,7 +6621,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B299">
@@ -6642,7 +6642,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B300">
@@ -6663,7 +6663,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B301">
@@ -6684,7 +6684,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B302">
@@ -6705,7 +6705,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B303">
@@ -6726,7 +6726,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B304">
@@ -6747,7 +6747,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B305">
@@ -6768,7 +6768,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B306">
@@ -6789,7 +6789,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B307">
@@ -6810,7 +6810,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B308">
@@ -6831,7 +6831,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B309">
@@ -6852,7 +6852,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B310">
@@ -6873,7 +6873,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B311">
@@ -6894,7 +6894,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B312">
@@ -6915,7 +6915,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B313">
@@ -6936,7 +6936,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B314">
@@ -6957,7 +6957,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B315">
@@ -6978,7 +6978,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B316">
@@ -6999,7 +6999,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B317">
@@ -7020,7 +7020,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B318">
@@ -7041,7 +7041,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B319">
@@ -7062,7 +7062,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B320">
@@ -7083,7 +7083,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B321">
@@ -7104,7 +7104,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B322">
@@ -7125,7 +7125,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B323">
@@ -7146,7 +7146,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B324">
@@ -7167,7 +7167,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B325">
@@ -7188,7 +7188,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B326">
@@ -7209,7 +7209,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B327">
@@ -7230,7 +7230,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B328">
@@ -7251,7 +7251,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B329">
@@ -7272,7 +7272,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B330">
@@ -7293,7 +7293,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B331">
@@ -8196,7 +8196,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B374">
@@ -8217,7 +8217,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B375">
@@ -8238,7 +8238,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B376">
@@ -8259,7 +8259,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B377">
@@ -8280,7 +8280,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B378">
@@ -8301,7 +8301,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B379">
@@ -8322,7 +8322,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B380">
@@ -8343,7 +8343,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B381">
@@ -8364,7 +8364,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B382">
@@ -8385,7 +8385,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B383">
@@ -8406,7 +8406,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B384">
@@ -8427,7 +8427,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B385">
@@ -8448,7 +8448,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B386">
@@ -8469,7 +8469,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B387">
@@ -8490,7 +8490,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B388">
@@ -8511,7 +8511,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B389">
@@ -8532,7 +8532,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B390">
@@ -8553,7 +8553,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B391">
@@ -8574,7 +8574,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B392">
@@ -8595,7 +8595,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B393">
@@ -8616,7 +8616,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B394">
@@ -8637,7 +8637,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B395">
@@ -8658,7 +8658,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B396">
@@ -8679,7 +8679,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B397">
@@ -8700,7 +8700,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B398">
@@ -8721,7 +8721,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B399">
@@ -8742,7 +8742,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B400">
@@ -8763,7 +8763,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B401">
@@ -8784,7 +8784,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B402">
@@ -8805,7 +8805,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B403">
@@ -8826,7 +8826,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B404">
@@ -8847,7 +8847,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B405">
@@ -8868,7 +8868,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B406">
@@ -8889,7 +8889,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B407">
@@ -8910,7 +8910,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B408">
@@ -8931,7 +8931,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B409">
@@ -8952,7 +8952,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B410">
@@ -8973,7 +8973,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B411">
@@ -8994,7 +8994,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B412">
@@ -9015,7 +9015,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B413">
@@ -9036,7 +9036,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B414">
@@ -9057,7 +9057,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B415">
@@ -9078,7 +9078,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B416">
@@ -9099,7 +9099,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B417">
@@ -9120,7 +9120,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B418">
@@ -9141,7 +9141,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B419">
@@ -9162,7 +9162,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B420">
@@ -9183,7 +9183,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B421">
@@ -9204,7 +9204,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B422">
@@ -9225,7 +9225,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B423">
@@ -9246,7 +9246,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B424">
@@ -10149,7 +10149,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B467">
@@ -10170,7 +10170,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B468">
@@ -10191,7 +10191,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B469">
@@ -10212,7 +10212,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B470">
@@ -10233,7 +10233,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B471">
@@ -10254,7 +10254,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B472">
@@ -10275,7 +10275,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B473">
@@ -10296,7 +10296,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B474">
@@ -10317,7 +10317,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B475">
@@ -10338,7 +10338,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B476">
@@ -10359,7 +10359,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B477">
@@ -10380,7 +10380,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B478">
@@ -10401,7 +10401,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B479">
@@ -10422,7 +10422,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B480">
@@ -10443,7 +10443,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B481">
@@ -10464,7 +10464,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B482">
@@ -10485,7 +10485,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B483">
@@ -10506,7 +10506,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B484">
@@ -10527,7 +10527,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B485">
@@ -10548,7 +10548,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B486">
@@ -10569,7 +10569,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B487">
@@ -10590,7 +10590,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B488">
@@ -10611,7 +10611,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B489">
@@ -10632,7 +10632,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B490">
@@ -10653,7 +10653,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B491">
@@ -10674,7 +10674,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B492">
@@ -10695,7 +10695,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B493">
@@ -10716,7 +10716,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B494">
@@ -10737,7 +10737,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B495">
@@ -10758,7 +10758,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B496">
@@ -10779,7 +10779,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B497">
@@ -10800,7 +10800,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B498">
@@ -10821,7 +10821,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B499">
@@ -10842,7 +10842,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B500">
@@ -10863,7 +10863,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B501">
@@ -10884,7 +10884,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B502">
@@ -10905,7 +10905,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B503">
@@ -10926,7 +10926,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B504">
@@ -10947,7 +10947,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B505">
@@ -10968,7 +10968,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B506">
@@ -10989,7 +10989,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B507">
@@ -11010,7 +11010,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B508">
@@ -11031,7 +11031,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B509">
@@ -11052,7 +11052,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B510">
@@ -11073,7 +11073,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B511">
@@ -11094,7 +11094,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B512">
@@ -11115,7 +11115,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B513">
@@ -11136,7 +11136,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B514">
@@ -11157,7 +11157,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B515">
@@ -11178,7 +11178,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B516">
@@ -11199,7 +11199,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B517">
@@ -12102,7 +12102,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B560">
@@ -12123,7 +12123,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B561">
@@ -12144,7 +12144,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B562">
@@ -12165,7 +12165,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B563">
@@ -12186,7 +12186,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B564">
@@ -12207,7 +12207,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B565">
@@ -12228,7 +12228,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B566">
@@ -12249,7 +12249,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B567">
@@ -12270,7 +12270,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B568">
@@ -12291,7 +12291,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B569">
@@ -12312,7 +12312,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B570">
@@ -12333,7 +12333,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B571">
@@ -12354,7 +12354,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B572">
@@ -12375,7 +12375,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B573">
@@ -12396,7 +12396,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B574">
@@ -12417,7 +12417,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B575">
@@ -12438,7 +12438,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B576">
@@ -12459,7 +12459,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B577">
@@ -12480,7 +12480,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B578">
@@ -12501,7 +12501,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B579">
@@ -12522,7 +12522,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B580">
@@ -12543,7 +12543,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B581">
@@ -12564,7 +12564,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B582">
@@ -12585,7 +12585,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B583">
@@ -12606,7 +12606,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B584">
@@ -12627,7 +12627,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B585">
@@ -12648,7 +12648,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B586">
@@ -12669,7 +12669,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B587">
@@ -12690,7 +12690,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B588">
@@ -12711,7 +12711,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B589">
@@ -12732,7 +12732,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B590">
@@ -12753,7 +12753,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B591">
@@ -12774,7 +12774,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B592">
@@ -12795,7 +12795,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B593">
@@ -12816,7 +12816,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B594">
@@ -12837,7 +12837,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B595">
@@ -12858,7 +12858,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B596">
@@ -12879,7 +12879,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B597">
@@ -12900,7 +12900,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B598">
@@ -12921,7 +12921,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B599">
@@ -12942,7 +12942,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B600">
@@ -12963,7 +12963,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B601">
@@ -12984,7 +12984,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B602">
@@ -13005,7 +13005,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B603">
@@ -13026,7 +13026,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B604">
@@ -13047,7 +13047,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B605">
@@ -13068,7 +13068,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B606">
@@ -13089,7 +13089,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B607">
@@ -13110,7 +13110,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B608">
@@ -13131,7 +13131,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B609">
@@ -13152,7 +13152,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B610">
@@ -14055,7 +14055,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B653">
@@ -14076,7 +14076,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B654">
@@ -14097,7 +14097,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B655">
@@ -14118,7 +14118,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B656">
@@ -14139,7 +14139,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B657">
@@ -14160,7 +14160,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B658">
@@ -14181,7 +14181,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B659">
@@ -14202,7 +14202,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B660">
@@ -14223,7 +14223,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B661">
@@ -14244,7 +14244,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B662">
@@ -14265,7 +14265,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B663">
@@ -14286,7 +14286,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B664">
@@ -14307,7 +14307,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B665">
@@ -14328,7 +14328,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B666">
@@ -14349,7 +14349,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B667">
@@ -14370,7 +14370,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B668">
@@ -14391,7 +14391,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B669">
@@ -14412,7 +14412,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B670">
@@ -14433,7 +14433,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B671">
@@ -14454,7 +14454,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B672">
@@ -14475,7 +14475,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B673">
@@ -14496,7 +14496,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B674">
@@ -14517,7 +14517,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B675">
@@ -14538,7 +14538,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B676">
@@ -14559,7 +14559,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B677">
@@ -14580,7 +14580,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B678">
@@ -14601,7 +14601,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B679">
@@ -14622,7 +14622,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B680">
@@ -14643,7 +14643,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B681">
@@ -14664,7 +14664,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B682">
@@ -14685,7 +14685,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B683">
@@ -14706,7 +14706,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B684">
@@ -14727,7 +14727,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B685">
@@ -14748,7 +14748,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B686">
@@ -14769,7 +14769,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B687">
@@ -14790,7 +14790,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B688">
@@ -14811,7 +14811,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B689">
@@ -14832,7 +14832,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B690">
@@ -14853,7 +14853,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B691">
@@ -14874,7 +14874,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B692">
@@ -14895,7 +14895,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B693">
@@ -14916,7 +14916,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B694">
@@ -14937,7 +14937,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B695">
@@ -14958,7 +14958,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B696">
@@ -14979,7 +14979,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B697">
@@ -15000,7 +15000,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B698">
@@ -15021,7 +15021,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B699">
@@ -15042,7 +15042,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B700">
@@ -15063,7 +15063,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B701">
@@ -15084,7 +15084,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B702">
@@ -15105,7 +15105,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B703">
@@ -16008,7 +16008,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B746">
@@ -16029,7 +16029,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B747">
@@ -16050,7 +16050,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B748">
@@ -16071,7 +16071,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B749">
@@ -16092,7 +16092,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B750">
@@ -16113,7 +16113,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B751">
@@ -16134,7 +16134,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B752">
@@ -16155,7 +16155,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B753">
@@ -16176,7 +16176,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B754">
@@ -16197,7 +16197,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B755">
@@ -16218,7 +16218,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B756">
@@ -16239,7 +16239,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B757">
@@ -16260,7 +16260,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B758">
@@ -16281,7 +16281,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B759">
@@ -16302,7 +16302,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B760">
@@ -16323,7 +16323,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B761">
@@ -16344,7 +16344,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B762">
@@ -16365,7 +16365,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B763">
@@ -16386,7 +16386,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B764">
@@ -16407,7 +16407,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B765">
@@ -16428,7 +16428,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B766">
@@ -16449,7 +16449,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B767">
@@ -16470,7 +16470,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B768">
@@ -16491,7 +16491,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B769">
@@ -16512,7 +16512,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B770">
@@ -16533,7 +16533,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B771">
@@ -16554,7 +16554,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B772">
@@ -16575,7 +16575,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B773">
@@ -16596,7 +16596,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B774">
@@ -16617,7 +16617,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B775">
@@ -16638,7 +16638,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B776">
@@ -16659,7 +16659,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B777">
@@ -16680,7 +16680,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B778">
@@ -16701,7 +16701,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B779">
@@ -16722,7 +16722,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B780">
@@ -16743,7 +16743,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B781">
@@ -16764,7 +16764,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B782">
@@ -16785,7 +16785,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B783">
@@ -16806,7 +16806,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B784">
@@ -16827,7 +16827,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B785">
@@ -16848,7 +16848,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B786">
@@ -16869,7 +16869,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B787">
@@ -16890,7 +16890,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B788">
@@ -16911,7 +16911,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B789">
@@ -16932,7 +16932,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B790">
@@ -16953,7 +16953,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B791">
@@ -16974,7 +16974,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B792">
@@ -16995,7 +16995,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B793">
@@ -17016,7 +17016,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B794">
@@ -17037,7 +17037,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B795">
@@ -17058,7 +17058,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B796">
@@ -17961,7 +17961,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B839">
@@ -17982,7 +17982,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B840">
@@ -18003,7 +18003,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B841">
@@ -18024,7 +18024,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B842">
@@ -18045,7 +18045,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B843">
@@ -18066,7 +18066,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B844">
@@ -18087,7 +18087,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B845">
@@ -18108,7 +18108,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B846">
@@ -18129,7 +18129,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B847">
@@ -18150,7 +18150,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B848">
@@ -18171,7 +18171,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B849">
@@ -18192,7 +18192,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B850">
@@ -18213,7 +18213,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B851">
@@ -18234,7 +18234,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B852">
@@ -18255,7 +18255,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B853">
@@ -18276,7 +18276,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B854">
@@ -18297,7 +18297,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B855">
@@ -18318,7 +18318,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B856">
@@ -18339,7 +18339,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B857">
@@ -18360,7 +18360,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B858">
@@ -18381,7 +18381,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B859">
@@ -18402,7 +18402,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B860">
@@ -18423,7 +18423,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B861">
@@ -18444,7 +18444,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B862">
@@ -18465,7 +18465,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B863">
@@ -18486,7 +18486,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B864">
@@ -18507,7 +18507,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B865">
@@ -18528,7 +18528,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B866">
@@ -18549,7 +18549,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B867">
@@ -18570,7 +18570,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B868">
@@ -18591,7 +18591,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B869">
@@ -18612,7 +18612,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B870">
@@ -18633,7 +18633,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B871">
@@ -18654,7 +18654,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B872">
@@ -18675,7 +18675,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B873">
@@ -18696,7 +18696,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B874">
@@ -18717,7 +18717,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B875">
@@ -18738,7 +18738,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B876">
@@ -18759,7 +18759,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B877">
@@ -18780,7 +18780,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B878">
@@ -18801,7 +18801,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B879">
@@ -18822,7 +18822,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B880">
@@ -18843,7 +18843,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B881">
@@ -18864,7 +18864,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B882">
@@ -18885,7 +18885,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B883">
@@ -18906,7 +18906,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B884">
@@ -18927,7 +18927,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B885">
@@ -18948,7 +18948,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B886">
@@ -18969,7 +18969,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B887">
@@ -18990,7 +18990,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B888">
@@ -19011,7 +19011,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B889">
@@ -19914,14 +19914,14 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>000</t>
         </is>
       </c>
       <c r="B932">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="C932">
-        <v>45427</v>
+        <v>44616</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -19929,20 +19929,20 @@
         </is>
       </c>
       <c r="E932">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B933">
-        <v>15.8</v>
+        <v>16.8</v>
       </c>
       <c r="C933">
-        <v>42994</v>
+        <v>43121</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -19950,20 +19950,20 @@
         </is>
       </c>
       <c r="E933">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B934">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="C934">
-        <v>47284</v>
+        <v>47014</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -19971,20 +19971,20 @@
         </is>
       </c>
       <c r="E934">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B935">
-        <v>9.6</v>
+        <v>12.8</v>
       </c>
       <c r="C935">
-        <v>49888</v>
+        <v>49045</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -19992,20 +19992,20 @@
         </is>
       </c>
       <c r="E935">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B936">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="C936">
-        <v>42994</v>
+        <v>47520</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -20013,20 +20013,20 @@
         </is>
       </c>
       <c r="E936">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B937">
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="C937">
-        <v>38371</v>
+        <v>38637</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -20034,20 +20034,20 @@
         </is>
       </c>
       <c r="E937">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B938">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="C938">
-        <v>66166</v>
+        <v>66023</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -20055,20 +20055,20 @@
         </is>
       </c>
       <c r="E938">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B939">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="C939">
-        <v>48388</v>
+        <v>46770</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -20076,20 +20076,20 @@
         </is>
       </c>
       <c r="E939">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B940">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="C940">
-        <v>48054</v>
+        <v>49966</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -20097,20 +20097,20 @@
         </is>
       </c>
       <c r="E940">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B941">
-        <v>13.8</v>
+        <v>16.7</v>
       </c>
       <c r="C941">
-        <v>43079</v>
+        <v>38859</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -20118,20 +20118,20 @@
         </is>
       </c>
       <c r="E941">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B942">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="C942">
-        <v>48284</v>
+        <v>44775</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -20139,20 +20139,20 @@
         </is>
       </c>
       <c r="E942">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B943">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="C943">
-        <v>42667</v>
+        <v>42233</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -20160,20 +20160,20 @@
         </is>
       </c>
       <c r="E943">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B944">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="C944">
-        <v>46315</v>
+        <v>47229</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -20181,20 +20181,20 @@
         </is>
       </c>
       <c r="E944">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B945">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C945">
-        <v>36811</v>
+        <v>39358</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -20202,20 +20202,20 @@
         </is>
       </c>
       <c r="E945">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B946">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="C946">
-        <v>41675</v>
+        <v>42318</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -20223,20 +20223,20 @@
         </is>
       </c>
       <c r="E946">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B947">
-        <v>8.9</v>
+        <v>10.1</v>
       </c>
       <c r="C947">
-        <v>55168</v>
+        <v>55817</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -20244,20 +20244,20 @@
         </is>
       </c>
       <c r="E947">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B948">
-        <v>12</v>
+        <v>13.6</v>
       </c>
       <c r="C948">
-        <v>45042</v>
+        <v>49551</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -20265,20 +20265,20 @@
         </is>
       </c>
       <c r="E948">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B949">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="C949">
-        <v>44702</v>
+        <v>46781</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -20286,20 +20286,20 @@
         </is>
       </c>
       <c r="E949">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B950">
-        <v>20.7</v>
+        <v>24.2</v>
       </c>
       <c r="C950">
-        <v>35935</v>
+        <v>36362</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -20307,20 +20307,20 @@
         </is>
       </c>
       <c r="E950">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B951">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="C951">
-        <v>54687</v>
+        <v>51885</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -20328,20 +20328,20 @@
         </is>
       </c>
       <c r="E951">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B952">
-        <v>14.4</v>
+        <v>17.2</v>
       </c>
       <c r="C952">
-        <v>43531</v>
+        <v>42168</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -20349,20 +20349,20 @@
         </is>
       </c>
       <c r="E952">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B953">
-        <v>17.8</v>
+        <v>17</v>
       </c>
       <c r="C953">
-        <v>35343</v>
+        <v>36734</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -20370,20 +20370,20 @@
         </is>
       </c>
       <c r="E953">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B954">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="C954">
-        <v>51812</v>
+        <v>49117</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -20391,20 +20391,20 @@
         </is>
       </c>
       <c r="E954">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B955">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="C955">
-        <v>43678</v>
+        <v>43947</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -20412,20 +20412,20 @@
         </is>
       </c>
       <c r="E955">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="956">
       <c r="A956" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B956">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="C956">
-        <v>49117</v>
+        <v>48938</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -20433,20 +20433,20 @@
         </is>
       </c>
       <c r="E956">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B957">
-        <v>11.9</v>
+        <v>13.8</v>
       </c>
       <c r="C957">
-        <v>39535</v>
+        <v>40856</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -20454,20 +20454,20 @@
         </is>
       </c>
       <c r="E957">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B958">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="C958">
-        <v>47446</v>
+        <v>45383</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -20475,20 +20475,20 @@
         </is>
       </c>
       <c r="E958">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B959">
-        <v>18.1</v>
+        <v>19.8</v>
       </c>
       <c r="C959">
-        <v>38629</v>
+        <v>35976</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -20496,20 +20496,20 @@
         </is>
       </c>
       <c r="E959">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B960">
-        <v>16.6</v>
+        <v>14</v>
       </c>
       <c r="C960">
-        <v>41394</v>
+        <v>41504</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -20517,20 +20517,20 @@
         </is>
       </c>
       <c r="E960">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B961">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="C961">
-        <v>76878</v>
+        <v>82054</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -20538,20 +20538,20 @@
         </is>
       </c>
       <c r="E961">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B962">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="C962">
-        <v>59652</v>
+        <v>62195</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -20559,20 +20559,20 @@
         </is>
       </c>
       <c r="E962">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B963">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="C963">
-        <v>48028</v>
+        <v>48775</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -20580,20 +20580,20 @@
         </is>
       </c>
       <c r="E963">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B964">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="C964">
-        <v>67011</v>
+        <v>66080</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -20601,20 +20601,20 @@
         </is>
       </c>
       <c r="E964">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B965">
-        <v>15</v>
+        <v>16.2</v>
       </c>
       <c r="C965">
-        <v>39989</v>
+        <v>40732</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -20622,20 +20622,20 @@
         </is>
       </c>
       <c r="E965">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B966">
-        <v>15.1</v>
+        <v>16</v>
       </c>
       <c r="C966">
-        <v>47108</v>
+        <v>41786</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -20643,20 +20643,20 @@
         </is>
       </c>
       <c r="E966">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B967">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="C967">
-        <v>44820</v>
+        <v>46530</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -20664,20 +20664,20 @@
         </is>
       </c>
       <c r="E967">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B968">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="C968">
-        <v>41861</v>
+        <v>46562</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -20685,20 +20685,20 @@
         </is>
       </c>
       <c r="E968">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B969">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="C969">
-        <v>53325</v>
+        <v>55267</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -20706,20 +20706,20 @@
         </is>
       </c>
       <c r="E969">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B970">
-        <v>16</v>
+        <v>15.6</v>
       </c>
       <c r="C970">
-        <v>38453</v>
+        <v>38117</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -20727,20 +20727,20 @@
         </is>
       </c>
       <c r="E970">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="971">
       <c r="A971" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B971">
-        <v>13.6</v>
+        <v>15.9</v>
       </c>
       <c r="C971">
-        <v>42204</v>
+        <v>41654</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -20748,20 +20748,20 @@
         </is>
       </c>
       <c r="E971">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B972">
-        <v>15.8</v>
+        <v>14.2</v>
       </c>
       <c r="C972">
-        <v>41588</v>
+        <v>41869</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -20769,20 +20769,20 @@
         </is>
       </c>
       <c r="E972">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B973">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="C973">
-        <v>57634</v>
+        <v>58695</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -20790,20 +20790,20 @@
         </is>
       </c>
       <c r="E973">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B974">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="C974">
-        <v>37805</v>
+        <v>39123</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -20811,20 +20811,20 @@
         </is>
       </c>
       <c r="E974">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B975">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
       <c r="C975">
-        <v>47152</v>
+        <v>47811</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -20832,20 +20832,20 @@
         </is>
       </c>
       <c r="E975">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="976">
       <c r="A976" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B976">
-        <v>13.2</v>
+        <v>16.1</v>
       </c>
       <c r="C976">
-        <v>45578</v>
+        <v>44151</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -20853,20 +20853,20 @@
         </is>
       </c>
       <c r="E976">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B977">
-        <v>16.4</v>
+        <v>17.7</v>
       </c>
       <c r="C977">
-        <v>47054</v>
+        <v>45252</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -20874,20 +20874,20 @@
         </is>
       </c>
       <c r="E977">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B978">
-        <v>14.5</v>
+        <v>16.2</v>
       </c>
       <c r="C978">
-        <v>46022</v>
+        <v>44039</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -20895,20 +20895,20 @@
         </is>
       </c>
       <c r="E978">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B979">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="C979">
-        <v>39398</v>
+        <v>41305</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -20916,20 +20916,20 @@
         </is>
       </c>
       <c r="E979">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B980">
-        <v>14.7</v>
+        <v>18</v>
       </c>
       <c r="C980">
-        <v>41774</v>
+        <v>39449</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -20937,20 +20937,20 @@
         </is>
       </c>
       <c r="E980">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B981">
-        <v>19.7</v>
+        <v>20.8</v>
       </c>
       <c r="C981">
-        <v>41201</v>
+        <v>39393</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -20958,20 +20958,20 @@
         </is>
       </c>
       <c r="E981">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B982">
-        <v>13.6</v>
+        <v>12.7</v>
       </c>
       <c r="C982">
-        <v>46767</v>
+        <v>43283</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         </is>
       </c>
       <c r="E982">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="983">
@@ -20989,10 +20989,10 @@
         </is>
       </c>
       <c r="B983">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="C983">
-        <v>42825</v>
+        <v>43854</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         </is>
       </c>
       <c r="E983">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="984">
@@ -21013,7 +21013,7 @@
         <v>17</v>
       </c>
       <c r="C984">
-        <v>39392</v>
+        <v>40466</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         </is>
       </c>
       <c r="E984">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="985">
@@ -21031,10 +21031,10 @@
         </is>
       </c>
       <c r="B985">
-        <v>21.9</v>
+        <v>24.3</v>
       </c>
       <c r="C985">
-        <v>36061</v>
+        <v>38348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         </is>
       </c>
       <c r="E985">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="986">
@@ -21052,10 +21052,10 @@
         </is>
       </c>
       <c r="B986">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="C986">
-        <v>47134</v>
+        <v>41853</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -21063,7 +21063,7 @@
         </is>
       </c>
       <c r="E986">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="987">
@@ -21073,10 +21073,10 @@
         </is>
       </c>
       <c r="B987">
-        <v>10.2</v>
+        <v>11.9</v>
       </c>
       <c r="C987">
-        <v>55411</v>
+        <v>53738</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         </is>
       </c>
       <c r="E987">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="988">
@@ -21094,10 +21094,10 @@
         </is>
       </c>
       <c r="B988">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="C988">
-        <v>47764</v>
+        <v>48043</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         </is>
       </c>
       <c r="E988">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="989">
@@ -21115,10 +21115,10 @@
         </is>
       </c>
       <c r="B989">
-        <v>13.9</v>
+        <v>12.6</v>
       </c>
       <c r="C989">
-        <v>43350</v>
+        <v>45269</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="E989">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="990">
@@ -21136,10 +21136,10 @@
         </is>
       </c>
       <c r="B990">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="C990">
-        <v>49541</v>
+        <v>47937</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="E990">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="991">
@@ -21157,10 +21157,10 @@
         </is>
       </c>
       <c r="B991">
-        <v>16.9</v>
+        <v>17.5</v>
       </c>
       <c r="C991">
-        <v>36620</v>
+        <v>35999</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         </is>
       </c>
       <c r="E991">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="992">
@@ -21178,10 +21178,10 @@
         </is>
       </c>
       <c r="B992">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="C992">
-        <v>41422</v>
+        <v>42658</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         </is>
       </c>
       <c r="E992">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="993">
@@ -21199,10 +21199,10 @@
         </is>
       </c>
       <c r="B993">
-        <v>15.7</v>
+        <v>16.6</v>
       </c>
       <c r="C993">
-        <v>41011</v>
+        <v>42749</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -21210,7 +21210,7 @@
         </is>
       </c>
       <c r="E993">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="994">
@@ -21220,10 +21220,10 @@
         </is>
       </c>
       <c r="B994">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C994">
-        <v>44652</v>
+        <v>41446</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
         </is>
       </c>
       <c r="E994">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="995">
@@ -21241,10 +21241,10 @@
         </is>
       </c>
       <c r="B995">
-        <v>11.8</v>
+        <v>14.7</v>
       </c>
       <c r="C995">
-        <v>40452</v>
+        <v>39684</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="E995">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="996">
@@ -21262,10 +21262,10 @@
         </is>
       </c>
       <c r="B996">
-        <v>7.6</v>
+        <v>10.9</v>
       </c>
       <c r="C996">
-        <v>60718</v>
+        <v>56648</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -21273,7 +21273,7 @@
         </is>
       </c>
       <c r="E996">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="997">
@@ -21283,10 +21283,10 @@
         </is>
       </c>
       <c r="B997">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C997">
-        <v>55517</v>
+        <v>56159</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         </is>
       </c>
       <c r="E997">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="998">
@@ -21304,10 +21304,10 @@
         </is>
       </c>
       <c r="B998">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="C998">
-        <v>44483</v>
+        <v>41794</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         </is>
       </c>
       <c r="E998">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="999">
@@ -21325,10 +21325,10 @@
         </is>
       </c>
       <c r="B999">
-        <v>13.1</v>
+        <v>13.9</v>
       </c>
       <c r="C999">
-        <v>47394</v>
+        <v>44437</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         </is>
       </c>
       <c r="E999">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1000">
@@ -21346,10 +21346,10 @@
         </is>
       </c>
       <c r="B1000">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="C1000">
-        <v>37021</v>
+        <v>40806</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="E1000">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1001">
@@ -21367,10 +21367,10 @@
         </is>
       </c>
       <c r="B1001">
-        <v>11.8</v>
+        <v>10.7</v>
       </c>
       <c r="C1001">
-        <v>44179</v>
+        <v>45951</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="E1001">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1002">
@@ -21388,10 +21388,10 @@
         </is>
       </c>
       <c r="B1002">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="C1002">
-        <v>43716</v>
+        <v>45464</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         </is>
       </c>
       <c r="E1002">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1003">
@@ -21409,10 +21409,10 @@
         </is>
       </c>
       <c r="B1003">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="C1003">
-        <v>43544</v>
+        <v>42316</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         </is>
       </c>
       <c r="E1003">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1004">
@@ -21430,10 +21430,10 @@
         </is>
       </c>
       <c r="B1004">
-        <v>16.6</v>
+        <v>18.8</v>
       </c>
       <c r="C1004">
-        <v>38812</v>
+        <v>39134</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -21441,7 +21441,7 @@
         </is>
       </c>
       <c r="E1004">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1005">
@@ -21451,10 +21451,10 @@
         </is>
       </c>
       <c r="B1005">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="C1005">
-        <v>50611</v>
+        <v>46619</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         </is>
       </c>
       <c r="E1005">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1006">
@@ -21472,10 +21472,10 @@
         </is>
       </c>
       <c r="B1006">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="C1006">
-        <v>49006</v>
+        <v>47726</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         </is>
       </c>
       <c r="E1006">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1007">
@@ -21493,10 +21493,10 @@
         </is>
       </c>
       <c r="B1007">
-        <v>13.8</v>
+        <v>18.2</v>
       </c>
       <c r="C1007">
-        <v>40369</v>
+        <v>38317</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="E1007">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1008">
@@ -21514,10 +21514,10 @@
         </is>
       </c>
       <c r="B1008">
-        <v>13.6</v>
+        <v>12.8</v>
       </c>
       <c r="C1008">
-        <v>45879</v>
+        <v>45431</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         </is>
       </c>
       <c r="E1008">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1009">
@@ -21535,10 +21535,10 @@
         </is>
       </c>
       <c r="B1009">
-        <v>17.1</v>
+        <v>14.7</v>
       </c>
       <c r="C1009">
-        <v>39091</v>
+        <v>42481</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         </is>
       </c>
       <c r="E1009">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1010">
@@ -21556,10 +21556,10 @@
         </is>
       </c>
       <c r="B1010">
-        <v>17.2</v>
+        <v>16.3</v>
       </c>
       <c r="C1010">
-        <v>41837</v>
+        <v>42268</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         </is>
       </c>
       <c r="E1010">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1011">
@@ -21580,7 +21580,7 @@
         <v>20.9</v>
       </c>
       <c r="C1011">
-        <v>41917</v>
+        <v>41722</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         </is>
       </c>
       <c r="E1011">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1012">
@@ -21598,10 +21598,10 @@
         </is>
       </c>
       <c r="B1012">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="C1012">
-        <v>52423</v>
+        <v>54171</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         </is>
       </c>
       <c r="E1012">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1013">
@@ -21619,10 +21619,10 @@
         </is>
       </c>
       <c r="B1013">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="C1013">
-        <v>43630</v>
+        <v>44337</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         </is>
       </c>
       <c r="E1013">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1014">
@@ -21640,10 +21640,10 @@
         </is>
       </c>
       <c r="B1014">
-        <v>15.2</v>
+        <v>16.9</v>
       </c>
       <c r="C1014">
-        <v>42404</v>
+        <v>41024</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="E1014">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1015">
@@ -21661,10 +21661,10 @@
         </is>
       </c>
       <c r="B1015">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="C1015">
-        <v>40164</v>
+        <v>42613</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         </is>
       </c>
       <c r="E1015">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1016">
@@ -21682,10 +21682,10 @@
         </is>
       </c>
       <c r="B1016">
-        <v>20.9</v>
+        <v>19.1</v>
       </c>
       <c r="C1016">
-        <v>37876</v>
+        <v>39089</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         </is>
       </c>
       <c r="E1016">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1017">
@@ -21703,10 +21703,10 @@
         </is>
       </c>
       <c r="B1017">
-        <v>13.9</v>
+        <v>12.2</v>
       </c>
       <c r="C1017">
-        <v>42076</v>
+        <v>42990</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         </is>
       </c>
       <c r="E1017">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1018">
@@ -21724,10 +21724,10 @@
         </is>
       </c>
       <c r="B1018">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C1018">
-        <v>50841</v>
+        <v>50349</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         </is>
       </c>
       <c r="E1018">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1019">
@@ -21745,10 +21745,10 @@
         </is>
       </c>
       <c r="B1019">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="C1019">
-        <v>58436</v>
+        <v>59195</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         </is>
       </c>
       <c r="E1019">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1020">
@@ -21766,10 +21766,10 @@
         </is>
       </c>
       <c r="B1020">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="C1020">
-        <v>40419</v>
+        <v>39945</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         </is>
       </c>
       <c r="E1020">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1021">
@@ -21787,10 +21787,10 @@
         </is>
       </c>
       <c r="B1021">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="C1021">
-        <v>38909</v>
+        <v>36424</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         </is>
       </c>
       <c r="E1021">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1022">
@@ -21808,10 +21808,10 @@
         </is>
       </c>
       <c r="B1022">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="C1022">
-        <v>48000</v>
+        <v>45492</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         </is>
       </c>
       <c r="E1022">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1023">
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="B1023">
-        <v>10.8</v>
+        <v>12.2</v>
       </c>
       <c r="C1023">
-        <v>46495</v>
+        <v>43487</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         </is>
       </c>
       <c r="E1023">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="1024">
@@ -21850,10 +21850,10 @@
         </is>
       </c>
       <c r="B1024">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="C1024">
-        <v>48451</v>
+        <v>49989</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -21861,1959 +21861,6 @@
         </is>
       </c>
       <c r="E1024">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B1025">
-        <v>15.3</v>
-      </c>
-      <c r="C1025">
-        <v>44616</v>
-      </c>
-      <c r="D1025" t="inlineStr">
-        <is>
-          <t>Indiana</t>
-        </is>
-      </c>
-      <c r="E1025">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B1026">
-        <v>16.8</v>
-      </c>
-      <c r="C1026">
-        <v>43121</v>
-      </c>
-      <c r="D1026" t="inlineStr">
-        <is>
-          <t>Adams County</t>
-        </is>
-      </c>
-      <c r="E1026">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B1027">
-        <v>13.9</v>
-      </c>
-      <c r="C1027">
-        <v>47014</v>
-      </c>
-      <c r="D1027" t="inlineStr">
-        <is>
-          <t>Allen County</t>
-        </is>
-      </c>
-      <c r="E1027">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B1028">
-        <v>12.8</v>
-      </c>
-      <c r="C1028">
-        <v>49045</v>
-      </c>
-      <c r="D1028" t="inlineStr">
-        <is>
-          <t>Bartholomew County</t>
-        </is>
-      </c>
-      <c r="E1028">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B1029">
-        <v>11.3</v>
-      </c>
-      <c r="C1029">
-        <v>47520</v>
-      </c>
-      <c r="D1029" t="inlineStr">
-        <is>
-          <t>Benton County</t>
-        </is>
-      </c>
-      <c r="E1029">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B1030">
-        <v>16</v>
-      </c>
-      <c r="C1030">
-        <v>38637</v>
-      </c>
-      <c r="D1030" t="inlineStr">
-        <is>
-          <t>Blackford County</t>
-        </is>
-      </c>
-      <c r="E1030">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B1031">
-        <v>8</v>
-      </c>
-      <c r="C1031">
-        <v>66023</v>
-      </c>
-      <c r="D1031" t="inlineStr">
-        <is>
-          <t>Boone County</t>
-        </is>
-      </c>
-      <c r="E1031">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B1032">
-        <v>13.2</v>
-      </c>
-      <c r="C1032">
-        <v>46770</v>
-      </c>
-      <c r="D1032" t="inlineStr">
-        <is>
-          <t>Brown County</t>
-        </is>
-      </c>
-      <c r="E1032">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B1033">
-        <v>10.1</v>
-      </c>
-      <c r="C1033">
-        <v>49966</v>
-      </c>
-      <c r="D1033" t="inlineStr">
-        <is>
-          <t>Carroll County</t>
-        </is>
-      </c>
-      <c r="E1033">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B1034">
-        <v>16.7</v>
-      </c>
-      <c r="C1034">
-        <v>38859</v>
-      </c>
-      <c r="D1034" t="inlineStr">
-        <is>
-          <t>Cass County</t>
-        </is>
-      </c>
-      <c r="E1034">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B1035">
-        <v>12.5</v>
-      </c>
-      <c r="C1035">
-        <v>44775</v>
-      </c>
-      <c r="D1035" t="inlineStr">
-        <is>
-          <t>Clark County</t>
-        </is>
-      </c>
-      <c r="E1035">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B1036">
-        <v>13.6</v>
-      </c>
-      <c r="C1036">
-        <v>42233</v>
-      </c>
-      <c r="D1036" t="inlineStr">
-        <is>
-          <t>Clay County</t>
-        </is>
-      </c>
-      <c r="E1036">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B1037">
-        <v>12.8</v>
-      </c>
-      <c r="C1037">
-        <v>47229</v>
-      </c>
-      <c r="D1037" t="inlineStr">
-        <is>
-          <t>Clinton County</t>
-        </is>
-      </c>
-      <c r="E1037">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B1038">
-        <v>17</v>
-      </c>
-      <c r="C1038">
-        <v>39358</v>
-      </c>
-      <c r="D1038" t="inlineStr">
-        <is>
-          <t>Crawford County</t>
-        </is>
-      </c>
-      <c r="E1038">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B1039">
-        <v>14.7</v>
-      </c>
-      <c r="C1039">
-        <v>42318</v>
-      </c>
-      <c r="D1039" t="inlineStr">
-        <is>
-          <t>Daviess County</t>
-        </is>
-      </c>
-      <c r="E1039">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B1040">
-        <v>10.1</v>
-      </c>
-      <c r="C1040">
-        <v>55817</v>
-      </c>
-      <c r="D1040" t="inlineStr">
-        <is>
-          <t>Dearborn County</t>
-        </is>
-      </c>
-      <c r="E1040">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B1041">
-        <v>13.6</v>
-      </c>
-      <c r="C1041">
-        <v>49551</v>
-      </c>
-      <c r="D1041" t="inlineStr">
-        <is>
-          <t>Decatur County</t>
-        </is>
-      </c>
-      <c r="E1041">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B1042">
-        <v>10.6</v>
-      </c>
-      <c r="C1042">
-        <v>46781</v>
-      </c>
-      <c r="D1042" t="inlineStr">
-        <is>
-          <t>De Kalb County</t>
-        </is>
-      </c>
-      <c r="E1042">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B1043">
-        <v>24.2</v>
-      </c>
-      <c r="C1043">
-        <v>36362</v>
-      </c>
-      <c r="D1043" t="inlineStr">
-        <is>
-          <t>Delaware County</t>
-        </is>
-      </c>
-      <c r="E1043">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B1044">
-        <v>8.4</v>
-      </c>
-      <c r="C1044">
-        <v>51885</v>
-      </c>
-      <c r="D1044" t="inlineStr">
-        <is>
-          <t>Dubois County</t>
-        </is>
-      </c>
-      <c r="E1044">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B1045">
-        <v>17.2</v>
-      </c>
-      <c r="C1045">
-        <v>42168</v>
-      </c>
-      <c r="D1045" t="inlineStr">
-        <is>
-          <t>Elkhart County</t>
-        </is>
-      </c>
-      <c r="E1045">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B1046">
-        <v>17</v>
-      </c>
-      <c r="C1046">
-        <v>36734</v>
-      </c>
-      <c r="D1046" t="inlineStr">
-        <is>
-          <t>Fayette County</t>
-        </is>
-      </c>
-      <c r="E1046">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="B1047">
-        <v>12.4</v>
-      </c>
-      <c r="C1047">
-        <v>49117</v>
-      </c>
-      <c r="D1047" t="inlineStr">
-        <is>
-          <t>Floyd County</t>
-        </is>
-      </c>
-      <c r="E1047">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="B1048">
-        <v>12.4</v>
-      </c>
-      <c r="C1048">
-        <v>43947</v>
-      </c>
-      <c r="D1048" t="inlineStr">
-        <is>
-          <t>Fountain County</t>
-        </is>
-      </c>
-      <c r="E1048">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="B1049">
-        <v>12.3</v>
-      </c>
-      <c r="C1049">
-        <v>48938</v>
-      </c>
-      <c r="D1049" t="inlineStr">
-        <is>
-          <t>Franklin County</t>
-        </is>
-      </c>
-      <c r="E1049">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="B1050">
-        <v>13.8</v>
-      </c>
-      <c r="C1050">
-        <v>40856</v>
-      </c>
-      <c r="D1050" t="inlineStr">
-        <is>
-          <t>Fulton County</t>
-        </is>
-      </c>
-      <c r="E1050">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B1051">
-        <v>12.1</v>
-      </c>
-      <c r="C1051">
-        <v>45383</v>
-      </c>
-      <c r="D1051" t="inlineStr">
-        <is>
-          <t>Gibson County</t>
-        </is>
-      </c>
-      <c r="E1051">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B1052">
-        <v>19.8</v>
-      </c>
-      <c r="C1052">
-        <v>35976</v>
-      </c>
-      <c r="D1052" t="inlineStr">
-        <is>
-          <t>Grant County</t>
-        </is>
-      </c>
-      <c r="E1052">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B1053">
-        <v>14</v>
-      </c>
-      <c r="C1053">
-        <v>41504</v>
-      </c>
-      <c r="D1053" t="inlineStr">
-        <is>
-          <t>Greene County</t>
-        </is>
-      </c>
-      <c r="E1053">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B1054">
-        <v>4.9</v>
-      </c>
-      <c r="C1054">
-        <v>82054</v>
-      </c>
-      <c r="D1054" t="inlineStr">
-        <is>
-          <t>Hamilton County</t>
-        </is>
-      </c>
-      <c r="E1054">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B1055">
-        <v>8.5</v>
-      </c>
-      <c r="C1055">
-        <v>62195</v>
-      </c>
-      <c r="D1055" t="inlineStr">
-        <is>
-          <t>Hancock County</t>
-        </is>
-      </c>
-      <c r="E1055">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B1056">
-        <v>11</v>
-      </c>
-      <c r="C1056">
-        <v>48775</v>
-      </c>
-      <c r="D1056" t="inlineStr">
-        <is>
-          <t>Harrison County</t>
-        </is>
-      </c>
-      <c r="E1056">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B1057">
-        <v>6.4</v>
-      </c>
-      <c r="C1057">
-        <v>66080</v>
-      </c>
-      <c r="D1057" t="inlineStr">
-        <is>
-          <t>Hendricks County</t>
-        </is>
-      </c>
-      <c r="E1057">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B1058">
-        <v>16.2</v>
-      </c>
-      <c r="C1058">
-        <v>40732</v>
-      </c>
-      <c r="D1058" t="inlineStr">
-        <is>
-          <t>Henry County</t>
-        </is>
-      </c>
-      <c r="E1058">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B1059">
-        <v>16</v>
-      </c>
-      <c r="C1059">
-        <v>41786</v>
-      </c>
-      <c r="D1059" t="inlineStr">
-        <is>
-          <t>Howard County</t>
-        </is>
-      </c>
-      <c r="E1059">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B1060">
-        <v>11.3</v>
-      </c>
-      <c r="C1060">
-        <v>46530</v>
-      </c>
-      <c r="D1060" t="inlineStr">
-        <is>
-          <t>Huntington County</t>
-        </is>
-      </c>
-      <c r="E1060">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B1061">
-        <v>12.7</v>
-      </c>
-      <c r="C1061">
-        <v>46562</v>
-      </c>
-      <c r="D1061" t="inlineStr">
-        <is>
-          <t>Jackson County</t>
-        </is>
-      </c>
-      <c r="E1061">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B1062">
-        <v>9.5</v>
-      </c>
-      <c r="C1062">
-        <v>55267</v>
-      </c>
-      <c r="D1062" t="inlineStr">
-        <is>
-          <t>Jasper County</t>
-        </is>
-      </c>
-      <c r="E1062">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B1063">
-        <v>15.6</v>
-      </c>
-      <c r="C1063">
-        <v>38117</v>
-      </c>
-      <c r="D1063" t="inlineStr">
-        <is>
-          <t>Jay County</t>
-        </is>
-      </c>
-      <c r="E1063">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B1064">
-        <v>15.9</v>
-      </c>
-      <c r="C1064">
-        <v>41654</v>
-      </c>
-      <c r="D1064" t="inlineStr">
-        <is>
-          <t>Jefferson County</t>
-        </is>
-      </c>
-      <c r="E1064">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B1065">
-        <v>14.2</v>
-      </c>
-      <c r="C1065">
-        <v>41869</v>
-      </c>
-      <c r="D1065" t="inlineStr">
-        <is>
-          <t>Jennings County</t>
-        </is>
-      </c>
-      <c r="E1065">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B1066">
-        <v>10.5</v>
-      </c>
-      <c r="C1066">
-        <v>58695</v>
-      </c>
-      <c r="D1066" t="inlineStr">
-        <is>
-          <t>Johnson County</t>
-        </is>
-      </c>
-      <c r="E1066">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B1067">
-        <v>17.6</v>
-      </c>
-      <c r="C1067">
-        <v>39123</v>
-      </c>
-      <c r="D1067" t="inlineStr">
-        <is>
-          <t>Knox County</t>
-        </is>
-      </c>
-      <c r="E1067">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B1068">
-        <v>13.4</v>
-      </c>
-      <c r="C1068">
-        <v>47811</v>
-      </c>
-      <c r="D1068" t="inlineStr">
-        <is>
-          <t>Kosciusko County</t>
-        </is>
-      </c>
-      <c r="E1068">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B1069">
-        <v>16.1</v>
-      </c>
-      <c r="C1069">
-        <v>44151</v>
-      </c>
-      <c r="D1069" t="inlineStr">
-        <is>
-          <t>Lagrange County</t>
-        </is>
-      </c>
-      <c r="E1069">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B1070">
-        <v>17.7</v>
-      </c>
-      <c r="C1070">
-        <v>45252</v>
-      </c>
-      <c r="D1070" t="inlineStr">
-        <is>
-          <t>Lake County</t>
-        </is>
-      </c>
-      <c r="E1070">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B1071">
-        <v>16.2</v>
-      </c>
-      <c r="C1071">
-        <v>44039</v>
-      </c>
-      <c r="D1071" t="inlineStr">
-        <is>
-          <t>La Porte County</t>
-        </is>
-      </c>
-      <c r="E1071">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B1072">
-        <v>15.2</v>
-      </c>
-      <c r="C1072">
-        <v>41305</v>
-      </c>
-      <c r="D1072" t="inlineStr">
-        <is>
-          <t>Lawrence County</t>
-        </is>
-      </c>
-      <c r="E1072">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B1073">
-        <v>18</v>
-      </c>
-      <c r="C1073">
-        <v>39449</v>
-      </c>
-      <c r="D1073" t="inlineStr">
-        <is>
-          <t>Madison County</t>
-        </is>
-      </c>
-      <c r="E1073">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B1074">
-        <v>20.8</v>
-      </c>
-      <c r="C1074">
-        <v>39393</v>
-      </c>
-      <c r="D1074" t="inlineStr">
-        <is>
-          <t>Marion County</t>
-        </is>
-      </c>
-      <c r="E1074">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B1075">
-        <v>12.7</v>
-      </c>
-      <c r="C1075">
-        <v>43283</v>
-      </c>
-      <c r="D1075" t="inlineStr">
-        <is>
-          <t>Marshall County</t>
-        </is>
-      </c>
-      <c r="E1075">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="B1076">
-        <v>13.2</v>
-      </c>
-      <c r="C1076">
-        <v>43854</v>
-      </c>
-      <c r="D1076" t="inlineStr">
-        <is>
-          <t>Martin County</t>
-        </is>
-      </c>
-      <c r="E1076">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="B1077">
-        <v>17</v>
-      </c>
-      <c r="C1077">
-        <v>40466</v>
-      </c>
-      <c r="D1077" t="inlineStr">
-        <is>
-          <t>Miami County</t>
-        </is>
-      </c>
-      <c r="E1077">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="B1078">
-        <v>24.3</v>
-      </c>
-      <c r="C1078">
-        <v>38348</v>
-      </c>
-      <c r="D1078" t="inlineStr">
-        <is>
-          <t>Monroe County</t>
-        </is>
-      </c>
-      <c r="E1078">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1079">
-      <c r="A1079" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="B1079">
-        <v>15.3</v>
-      </c>
-      <c r="C1079">
-        <v>41853</v>
-      </c>
-      <c r="D1079" t="inlineStr">
-        <is>
-          <t>Montgomery County</t>
-        </is>
-      </c>
-      <c r="E1079">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1080">
-      <c r="A1080" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="B1080">
-        <v>11.9</v>
-      </c>
-      <c r="C1080">
-        <v>53738</v>
-      </c>
-      <c r="D1080" t="inlineStr">
-        <is>
-          <t>Morgan County</t>
-        </is>
-      </c>
-      <c r="E1080">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1081">
-      <c r="A1081" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="B1081">
-        <v>11.1</v>
-      </c>
-      <c r="C1081">
-        <v>48043</v>
-      </c>
-      <c r="D1081" t="inlineStr">
-        <is>
-          <t>Newton County</t>
-        </is>
-      </c>
-      <c r="E1081">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1082">
-      <c r="A1082" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="B1082">
-        <v>12.6</v>
-      </c>
-      <c r="C1082">
-        <v>45269</v>
-      </c>
-      <c r="D1082" t="inlineStr">
-        <is>
-          <t>Noble County</t>
-        </is>
-      </c>
-      <c r="E1082">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1083">
-      <c r="A1083" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="B1083">
-        <v>10</v>
-      </c>
-      <c r="C1083">
-        <v>47937</v>
-      </c>
-      <c r="D1083" t="inlineStr">
-        <is>
-          <t>Ohio County</t>
-        </is>
-      </c>
-      <c r="E1083">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1084">
-      <c r="A1084" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="B1084">
-        <v>17.5</v>
-      </c>
-      <c r="C1084">
-        <v>35999</v>
-      </c>
-      <c r="D1084" t="inlineStr">
-        <is>
-          <t>Orange County</t>
-        </is>
-      </c>
-      <c r="E1084">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="B1085">
-        <v>14.1</v>
-      </c>
-      <c r="C1085">
-        <v>42658</v>
-      </c>
-      <c r="D1085" t="inlineStr">
-        <is>
-          <t>Owen County</t>
-        </is>
-      </c>
-      <c r="E1085">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="B1086">
-        <v>16.6</v>
-      </c>
-      <c r="C1086">
-        <v>42749</v>
-      </c>
-      <c r="D1086" t="inlineStr">
-        <is>
-          <t>Parke County</t>
-        </is>
-      </c>
-      <c r="E1086">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="B1087">
-        <v>13</v>
-      </c>
-      <c r="C1087">
-        <v>41446</v>
-      </c>
-      <c r="D1087" t="inlineStr">
-        <is>
-          <t>Perry County</t>
-        </is>
-      </c>
-      <c r="E1087">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="B1088">
-        <v>14.7</v>
-      </c>
-      <c r="C1088">
-        <v>39684</v>
-      </c>
-      <c r="D1088" t="inlineStr">
-        <is>
-          <t>Pike County</t>
-        </is>
-      </c>
-      <c r="E1088">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="B1089">
-        <v>10.9</v>
-      </c>
-      <c r="C1089">
-        <v>56648</v>
-      </c>
-      <c r="D1089" t="inlineStr">
-        <is>
-          <t>Porter County</t>
-        </is>
-      </c>
-      <c r="E1089">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="B1090">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="C1090">
-        <v>56159</v>
-      </c>
-      <c r="D1090" t="inlineStr">
-        <is>
-          <t>Posey County</t>
-        </is>
-      </c>
-      <c r="E1090">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="B1091">
-        <v>14.2</v>
-      </c>
-      <c r="C1091">
-        <v>41794</v>
-      </c>
-      <c r="D1091" t="inlineStr">
-        <is>
-          <t>Pulaski County</t>
-        </is>
-      </c>
-      <c r="E1091">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1092">
-      <c r="A1092" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="B1092">
-        <v>13.9</v>
-      </c>
-      <c r="C1092">
-        <v>44437</v>
-      </c>
-      <c r="D1092" t="inlineStr">
-        <is>
-          <t>Putnam County</t>
-        </is>
-      </c>
-      <c r="E1092">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1093">
-      <c r="A1093" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="B1093">
-        <v>16</v>
-      </c>
-      <c r="C1093">
-        <v>40806</v>
-      </c>
-      <c r="D1093" t="inlineStr">
-        <is>
-          <t>Randolph County</t>
-        </is>
-      </c>
-      <c r="E1093">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1094">
-      <c r="A1094" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="B1094">
-        <v>10.7</v>
-      </c>
-      <c r="C1094">
-        <v>45951</v>
-      </c>
-      <c r="D1094" t="inlineStr">
-        <is>
-          <t>Ripley County</t>
-        </is>
-      </c>
-      <c r="E1094">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1095">
-      <c r="A1095" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="B1095">
-        <v>13.2</v>
-      </c>
-      <c r="C1095">
-        <v>45464</v>
-      </c>
-      <c r="D1095" t="inlineStr">
-        <is>
-          <t>Rush County</t>
-        </is>
-      </c>
-      <c r="E1095">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1096">
-      <c r="A1096" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="B1096">
-        <v>15.9</v>
-      </c>
-      <c r="C1096">
-        <v>42316</v>
-      </c>
-      <c r="D1096" t="inlineStr">
-        <is>
-          <t>St. Joseph County</t>
-        </is>
-      </c>
-      <c r="E1096">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1097">
-      <c r="A1097" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="B1097">
-        <v>18.8</v>
-      </c>
-      <c r="C1097">
-        <v>39134</v>
-      </c>
-      <c r="D1097" t="inlineStr">
-        <is>
-          <t>Scott County</t>
-        </is>
-      </c>
-      <c r="E1097">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1098">
-      <c r="A1098" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="B1098">
-        <v>12.8</v>
-      </c>
-      <c r="C1098">
-        <v>46619</v>
-      </c>
-      <c r="D1098" t="inlineStr">
-        <is>
-          <t>Shelby County</t>
-        </is>
-      </c>
-      <c r="E1098">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1099">
-      <c r="A1099" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="B1099">
-        <v>11.3</v>
-      </c>
-      <c r="C1099">
-        <v>47726</v>
-      </c>
-      <c r="D1099" t="inlineStr">
-        <is>
-          <t>Spencer County</t>
-        </is>
-      </c>
-      <c r="E1099">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1100">
-      <c r="A1100" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="B1100">
-        <v>18.2</v>
-      </c>
-      <c r="C1100">
-        <v>38317</v>
-      </c>
-      <c r="D1100" t="inlineStr">
-        <is>
-          <t>Starke County</t>
-        </is>
-      </c>
-      <c r="E1100">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1101">
-      <c r="A1101" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="B1101">
-        <v>12.8</v>
-      </c>
-      <c r="C1101">
-        <v>45431</v>
-      </c>
-      <c r="D1101" t="inlineStr">
-        <is>
-          <t>Steuben County</t>
-        </is>
-      </c>
-      <c r="E1101">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1102">
-      <c r="A1102" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="B1102">
-        <v>14.7</v>
-      </c>
-      <c r="C1102">
-        <v>42481</v>
-      </c>
-      <c r="D1102" t="inlineStr">
-        <is>
-          <t>Sullivan County</t>
-        </is>
-      </c>
-      <c r="E1102">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1103">
-      <c r="A1103" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="B1103">
-        <v>16.3</v>
-      </c>
-      <c r="C1103">
-        <v>42268</v>
-      </c>
-      <c r="D1103" t="inlineStr">
-        <is>
-          <t>Switzerland County</t>
-        </is>
-      </c>
-      <c r="E1103">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1104">
-      <c r="A1104" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="B1104">
-        <v>20.9</v>
-      </c>
-      <c r="C1104">
-        <v>41722</v>
-      </c>
-      <c r="D1104" t="inlineStr">
-        <is>
-          <t>Tippecanoe County</t>
-        </is>
-      </c>
-      <c r="E1104">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1105">
-      <c r="A1105" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="B1105">
-        <v>8.5</v>
-      </c>
-      <c r="C1105">
-        <v>54171</v>
-      </c>
-      <c r="D1105" t="inlineStr">
-        <is>
-          <t>Tipton County</t>
-        </is>
-      </c>
-      <c r="E1105">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1106">
-      <c r="A1106" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="B1106">
-        <v>12.6</v>
-      </c>
-      <c r="C1106">
-        <v>44337</v>
-      </c>
-      <c r="D1106" t="inlineStr">
-        <is>
-          <t>Union County</t>
-        </is>
-      </c>
-      <c r="E1106">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1107">
-      <c r="A1107" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="B1107">
-        <v>16.9</v>
-      </c>
-      <c r="C1107">
-        <v>41024</v>
-      </c>
-      <c r="D1107" t="inlineStr">
-        <is>
-          <t>Vanderburgh County</t>
-        </is>
-      </c>
-      <c r="E1107">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1108">
-      <c r="A1108" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="B1108">
-        <v>13.6</v>
-      </c>
-      <c r="C1108">
-        <v>42613</v>
-      </c>
-      <c r="D1108" t="inlineStr">
-        <is>
-          <t>Vermillion County</t>
-        </is>
-      </c>
-      <c r="E1108">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1109">
-      <c r="A1109" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="B1109">
-        <v>19.1</v>
-      </c>
-      <c r="C1109">
-        <v>39089</v>
-      </c>
-      <c r="D1109" t="inlineStr">
-        <is>
-          <t>Vigo County</t>
-        </is>
-      </c>
-      <c r="E1109">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1110">
-      <c r="A1110" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="B1110">
-        <v>12.2</v>
-      </c>
-      <c r="C1110">
-        <v>42990</v>
-      </c>
-      <c r="D1110" t="inlineStr">
-        <is>
-          <t>Wabash County</t>
-        </is>
-      </c>
-      <c r="E1110">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1111">
-      <c r="A1111" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="B1111">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="C1111">
-        <v>50349</v>
-      </c>
-      <c r="D1111" t="inlineStr">
-        <is>
-          <t>Warren County</t>
-        </is>
-      </c>
-      <c r="E1111">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1112">
-      <c r="A1112" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="B1112">
-        <v>7.3</v>
-      </c>
-      <c r="C1112">
-        <v>59195</v>
-      </c>
-      <c r="D1112" t="inlineStr">
-        <is>
-          <t>Warrick County</t>
-        </is>
-      </c>
-      <c r="E1112">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1113">
-      <c r="A1113" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="B1113">
-        <v>15.9</v>
-      </c>
-      <c r="C1113">
-        <v>39945</v>
-      </c>
-      <c r="D1113" t="inlineStr">
-        <is>
-          <t>Washington County</t>
-        </is>
-      </c>
-      <c r="E1113">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1114">
-      <c r="A1114" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="B1114">
-        <v>20.3</v>
-      </c>
-      <c r="C1114">
-        <v>36424</v>
-      </c>
-      <c r="D1114" t="inlineStr">
-        <is>
-          <t>Wayne County</t>
-        </is>
-      </c>
-      <c r="E1114">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1115">
-      <c r="A1115" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="B1115">
-        <v>9.6</v>
-      </c>
-      <c r="C1115">
-        <v>45492</v>
-      </c>
-      <c r="D1115" t="inlineStr">
-        <is>
-          <t>Wells County</t>
-        </is>
-      </c>
-      <c r="E1115">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1116">
-      <c r="A1116" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="B1116">
-        <v>12.2</v>
-      </c>
-      <c r="C1116">
-        <v>43487</v>
-      </c>
-      <c r="D1116" t="inlineStr">
-        <is>
-          <t>White County</t>
-        </is>
-      </c>
-      <c r="E1116">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="1117">
-      <c r="A1117" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="B1117">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="C1117">
-        <v>49989</v>
-      </c>
-      <c r="D1117" t="inlineStr">
-        <is>
-          <t>Whitley County</t>
-        </is>
-      </c>
-      <c r="E1117">
         <v>2010</v>
       </c>
     </row>

--- a/saipe_2000_2010.xlsx
+++ b/saipe_2000_2010.xlsx
@@ -388,7 +388,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C2">
         <v>41511</v>
@@ -409,7 +409,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C3">
         <v>42190</v>
@@ -430,7 +430,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C4">
         <v>44365</v>
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C5">
         <v>46301</v>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C6">
         <v>41085</v>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C7">
         <v>36319</v>
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.3</v>
+        <v>0.053</v>
       </c>
       <c r="C8">
         <v>54615</v>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C9">
         <v>46154</v>
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C10">
         <v>44687</v>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C11">
         <v>39512</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C12">
         <v>41039</v>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C13">
         <v>38197</v>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C14">
         <v>41586</v>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C15">
         <v>33770</v>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C16">
         <v>35218</v>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>6.3</v>
+        <v>0.063</v>
       </c>
       <c r="C17">
         <v>50547</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C18">
         <v>42495</v>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C19">
         <v>46357</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C20">
         <v>35791</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>4.5</v>
+        <v>0.045</v>
       </c>
       <c r="C21">
         <v>46484</v>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C22">
         <v>44986</v>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C23">
         <v>39133</v>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C24">
         <v>44789</v>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C25">
         <v>39486</v>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C26">
         <v>45385</v>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C27">
         <v>39280</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C28">
         <v>39438</v>
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C29">
         <v>36741</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C30">
         <v>35155</v>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>3.1</v>
+        <v>0.031</v>
       </c>
       <c r="C31">
         <v>76478</v>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>4.4</v>
+        <v>0.044</v>
       </c>
       <c r="C32">
         <v>57384</v>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C33">
         <v>44606</v>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>3.9</v>
+        <v>0.039</v>
       </c>
       <c r="C34">
         <v>58193</v>
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C35">
         <v>39726</v>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C36">
         <v>45800</v>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>6.6</v>
+        <v>0.066</v>
       </c>
       <c r="C37">
         <v>43091</v>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C38">
         <v>40700</v>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>6.9</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C39">
         <v>45118</v>
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C40">
         <v>36412</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C41">
         <v>38566</v>
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C42">
         <v>39514</v>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C43">
         <v>53930</v>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C44">
         <v>32454</v>
@@ -1291,7 +1291,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>6.3</v>
+        <v>0.063</v>
       </c>
       <c r="C45">
         <v>45539</v>
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C46">
         <v>44096</v>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C47">
         <v>41529</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C48">
         <v>40926</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C49">
         <v>37743</v>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C50">
         <v>39690</v>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C51">
         <v>41304</v>
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C52">
         <v>42947</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C53">
         <v>37656</v>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C54">
         <v>39991</v>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="B55">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C55">
         <v>35453</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C56">
         <v>42027</v>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C57">
         <v>49387</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C58">
         <v>41611</v>
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C59">
         <v>43793</v>
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>6.7</v>
+        <v>0.067</v>
       </c>
       <c r="C60">
         <v>41973</v>
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C61">
         <v>32787</v>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C62">
         <v>36885</v>
@@ -1669,7 +1669,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C63">
         <v>36360</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C64">
         <v>37549</v>
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C65">
         <v>36581</v>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C66">
         <v>54648</v>
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>6.9</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C67">
         <v>46852</v>
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C68">
         <v>36898</v>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="B69">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C69">
         <v>40328</v>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="B70">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C70">
         <v>36257</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C71">
         <v>43174</v>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="B72">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C72">
         <v>39568</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C73">
         <v>40952</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="B74">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C74">
         <v>35699</v>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C75">
         <v>44473</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C76">
         <v>43805</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C77">
         <v>37130</v>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C78">
         <v>44571</v>
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C79">
         <v>33803</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="B80">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C80">
         <v>36483</v>
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="B81">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C81">
         <v>40097</v>
@@ -2068,7 +2068,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>5.9</v>
+        <v>0.059</v>
       </c>
       <c r="C82">
         <v>49539</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B83">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C83">
         <v>37700</v>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C84">
         <v>38691</v>
@@ -2131,7 +2131,7 @@
         </is>
       </c>
       <c r="B85">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C85">
         <v>36703</v>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="B86">
-        <v>13.1</v>
+        <v>0.131</v>
       </c>
       <c r="C86">
         <v>34145</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="B87">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C87">
         <v>41241</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="B88">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C88">
         <v>42718</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B89">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C89">
         <v>51251</v>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="B90">
-        <v>9.9</v>
+        <v>0.099</v>
       </c>
       <c r="C90">
         <v>37758</v>
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B91">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C91">
         <v>36157</v>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>5.9</v>
+        <v>0.059</v>
       </c>
       <c r="C92">
         <v>44747</v>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B93">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C93">
         <v>41530</v>
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="B94">
-        <v>5.3</v>
+        <v>0.053</v>
       </c>
       <c r="C94">
         <v>47512</v>
@@ -2341,7 +2341,7 @@
         </is>
       </c>
       <c r="B95">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C95">
         <v>42073</v>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="B96">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C96">
         <v>41445</v>
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C97">
         <v>43519</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="B98">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C98">
         <v>45332</v>
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C99">
         <v>40618</v>
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C100">
         <v>35541</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B101">
-        <v>5.2</v>
+        <v>0.052</v>
       </c>
       <c r="C101">
         <v>55291</v>
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="B102">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C102">
         <v>45617</v>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C103">
         <v>44616</v>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="B104">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C104">
         <v>38554</v>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C105">
         <v>40280</v>
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C106">
         <v>37299</v>
@@ -2593,7 +2593,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C107">
         <v>40857</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="B108">
-        <v>13.1</v>
+        <v>0.131</v>
       </c>
       <c r="C108">
         <v>32855</v>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C109">
         <v>34725</v>
@@ -2656,7 +2656,7 @@
         </is>
       </c>
       <c r="B110">
-        <v>6.2</v>
+        <v>0.062</v>
       </c>
       <c r="C110">
         <v>49944</v>
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="B111">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C111">
         <v>41806</v>
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C112">
         <v>45424</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="B113">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C113">
         <v>34937</v>
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="C114">
         <v>46242</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B115">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C115">
         <v>43800</v>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C116">
         <v>38064</v>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="B117">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C117">
         <v>44454</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C118">
         <v>38852</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B119">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C119">
         <v>45792</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B120">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C120">
         <v>38705</v>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B121">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C121">
         <v>38943</v>
@@ -2908,7 +2908,7 @@
         </is>
       </c>
       <c r="B122">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C122">
         <v>35887</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="B123">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C123">
         <v>34724</v>
@@ -2950,7 +2950,7 @@
         </is>
       </c>
       <c r="B124">
-        <v>3.2</v>
+        <v>0.032</v>
       </c>
       <c r="C124">
         <v>77949</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="B125">
-        <v>4.6</v>
+        <v>0.046</v>
       </c>
       <c r="C125">
         <v>57258</v>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="B126">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C126">
         <v>44069</v>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="B127">
-        <v>4</v>
+        <v>0.04</v>
       </c>
       <c r="C127">
         <v>57918</v>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="B128">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C128">
         <v>39024</v>
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B129">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C129">
         <v>44440</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="B130">
-        <v>6.9</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C130">
         <v>42435</v>
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="B131">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C131">
         <v>40034</v>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="B132">
-        <v>6.9</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C132">
         <v>45017</v>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="B133">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C133">
         <v>35388</v>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="B134">
-        <v>9.9</v>
+        <v>0.099</v>
       </c>
       <c r="C134">
         <v>37750</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="B135">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C135">
         <v>38349</v>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="B136">
-        <v>6</v>
+        <v>0.06</v>
       </c>
       <c r="C136">
         <v>53323</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="B137">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C137">
         <v>32051</v>
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="B138">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C138">
         <v>44987</v>
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="B139">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C139">
         <v>42743</v>
@@ -3286,7 +3286,7 @@
         </is>
       </c>
       <c r="B140">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C140">
         <v>40530</v>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="B141">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C141">
         <v>39908</v>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="B142">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C142">
         <v>37183</v>
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="B143">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C143">
         <v>38799</v>
@@ -3370,7 +3370,7 @@
         </is>
       </c>
       <c r="B144">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C144">
         <v>40233</v>
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="B145">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C145">
         <v>41979</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="B146">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C146">
         <v>37054</v>
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="B147">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C147">
         <v>39019</v>
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="B148">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C148">
         <v>34748</v>
@@ -3475,7 +3475,7 @@
         </is>
       </c>
       <c r="B149">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C149">
         <v>41286</v>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="B150">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C150">
         <v>48815</v>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="B151">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C151">
         <v>41068</v>
@@ -3538,7 +3538,7 @@
         </is>
       </c>
       <c r="B152">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C152">
         <v>42697</v>
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C153">
         <v>41921</v>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="B154">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C154">
         <v>32085</v>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="B155">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C155">
         <v>36528</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="B156">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C156">
         <v>35456</v>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B157">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C157">
         <v>36787</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="B158">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C158">
         <v>35694</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="B159">
-        <v>5.9</v>
+        <v>0.059</v>
       </c>
       <c r="C159">
         <v>54163</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="B160">
-        <v>6.7</v>
+        <v>0.067</v>
       </c>
       <c r="C160">
         <v>47007</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B161">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C161">
         <v>36865</v>
@@ -3748,7 +3748,7 @@
         </is>
       </c>
       <c r="B162">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C162">
         <v>40394</v>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="B163">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C163">
         <v>35947</v>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="B164">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C164">
         <v>41727</v>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="B165">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C165">
         <v>39341</v>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="B166">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C166">
         <v>39655</v>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="B167">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C167">
         <v>34693</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="B168">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C168">
         <v>43988</v>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B169">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C169">
         <v>43197</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="B170">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C170">
         <v>36105</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="B171">
-        <v>6.6</v>
+        <v>0.066</v>
       </c>
       <c r="C171">
         <v>43346</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="B172">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C172">
         <v>33016</v>
@@ -3979,7 +3979,7 @@
         </is>
       </c>
       <c r="B173">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C173">
         <v>36116</v>
@@ -4000,7 +4000,7 @@
         </is>
       </c>
       <c r="B174">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C174">
         <v>39413</v>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="B175">
-        <v>6.1</v>
+        <v>0.061</v>
       </c>
       <c r="C175">
         <v>48652</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="B176">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C176">
         <v>37356</v>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="B177">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C177">
         <v>37725</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B178">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C178">
         <v>36230</v>
@@ -4105,7 +4105,7 @@
         </is>
       </c>
       <c r="B179">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C179">
         <v>33330</v>
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="B180">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C180">
         <v>40421</v>
@@ -4147,7 +4147,7 @@
         </is>
       </c>
       <c r="B181">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C181">
         <v>42673</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="B182">
-        <v>5.8</v>
+        <v>0.058</v>
       </c>
       <c r="C182">
         <v>51066</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B183">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C183">
         <v>36700</v>
@@ -4210,7 +4210,7 @@
         </is>
       </c>
       <c r="B184">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C184">
         <v>35372</v>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="B185">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C185">
         <v>43693</v>
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="B186">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C186">
         <v>40301</v>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="B187">
-        <v>5.6</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="C187">
         <v>46701</v>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="B188">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C188">
         <v>41973</v>
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="B189">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C189">
         <v>41489</v>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="B190">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C190">
         <v>43077</v>
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B191">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C191">
         <v>45300</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="B192">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C192">
         <v>40134</v>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="B193">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C193">
         <v>35907</v>
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="B194">
-        <v>5.3</v>
+        <v>0.053</v>
       </c>
       <c r="C194">
         <v>56746</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="B195">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C195">
         <v>46134</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="B196">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C196">
         <v>44608</v>
@@ -4483,7 +4483,7 @@
         </is>
       </c>
       <c r="B197">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C197">
         <v>38446</v>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="B198">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C198">
         <v>40301</v>
@@ -4525,7 +4525,7 @@
         </is>
       </c>
       <c r="B199">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C199">
         <v>37665</v>
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="B200">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C200">
         <v>40785</v>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B201">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C201">
         <v>33306</v>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="B202">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C202">
         <v>34749</v>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="B203">
-        <v>6.3</v>
+        <v>0.063</v>
       </c>
       <c r="C203">
         <v>51194</v>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="B204">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C204">
         <v>42653</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="B205">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C205">
         <v>45833</v>
@@ -4672,7 +4672,7 @@
         </is>
       </c>
       <c r="B206">
-        <v>12.8</v>
+        <v>0.128</v>
       </c>
       <c r="C206">
         <v>34810</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="B207">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="C207">
         <v>47638</v>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="B208">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C208">
         <v>43982</v>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B209">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C209">
         <v>38136</v>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="B210">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C210">
         <v>44452</v>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B211">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C211">
         <v>38777</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="B212">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C212">
         <v>46420</v>
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="B213">
-        <v>9.9</v>
+        <v>0.099</v>
       </c>
       <c r="C213">
         <v>38900</v>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="B214">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C214">
         <v>40024</v>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="B215">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C215">
         <v>35954</v>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="B216">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C216">
         <v>35391</v>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="B217">
-        <v>3.5</v>
+        <v>0.035</v>
       </c>
       <c r="C217">
         <v>80818</v>
@@ -4924,7 +4924,7 @@
         </is>
       </c>
       <c r="B218">
-        <v>4.8</v>
+        <v>0.048</v>
       </c>
       <c r="C218">
         <v>58477</v>
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="B219">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C219">
         <v>44606</v>
@@ -4966,7 +4966,7 @@
         </is>
       </c>
       <c r="B220">
-        <v>4.1</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="C220">
         <v>59917</v>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="B221">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C221">
         <v>39438</v>
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="B222">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C222">
         <v>44442</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="B223">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C223">
         <v>42277</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="B224">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C224">
         <v>40359</v>
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="B225">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C225">
         <v>45493</v>
@@ -5092,7 +5092,7 @@
         </is>
       </c>
       <c r="B226">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C226">
         <v>35196</v>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="B227">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C227">
         <v>38325</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="B228">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C228">
         <v>38406</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="B229">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C229">
         <v>53775</v>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="B230">
-        <v>13.7</v>
+        <v>0.137</v>
       </c>
       <c r="C230">
         <v>32476</v>
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="B231">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C231">
         <v>45428</v>
@@ -5218,7 +5218,7 @@
         </is>
       </c>
       <c r="B232">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C232">
         <v>43389</v>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="B233">
-        <v>12.1</v>
+        <v>0.121</v>
       </c>
       <c r="C233">
         <v>40169</v>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="B234">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C234">
         <v>39692</v>
@@ -5281,7 +5281,7 @@
         </is>
       </c>
       <c r="B235">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C235">
         <v>37782</v>
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="B236">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C236">
         <v>38973</v>
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="B237">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C237">
         <v>40458</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="B238">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C238">
         <v>41853</v>
@@ -5365,7 +5365,7 @@
         </is>
       </c>
       <c r="B239">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C239">
         <v>37188</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="B240">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C240">
         <v>39092</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="B241">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C241">
         <v>34782</v>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="B242">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C242">
         <v>41225</v>
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="B243">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C243">
         <v>49025</v>
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="B244">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C244">
         <v>40932</v>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="B245">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C245">
         <v>42934</v>
@@ -5512,7 +5512,7 @@
         </is>
       </c>
       <c r="B246">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C246">
         <v>42395</v>
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="B247">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C247">
         <v>32145</v>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="B248">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C248">
         <v>36887</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B249">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C249">
         <v>35258</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="B250">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C250">
         <v>37284</v>
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="B251">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C251">
         <v>36071</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="B252">
-        <v>6.5</v>
+        <v>0.065</v>
       </c>
       <c r="C252">
         <v>53726</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="B253">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C253">
         <v>48049</v>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="B254">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C254">
         <v>36957</v>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="B255">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C255">
         <v>40933</v>
@@ -5722,7 +5722,7 @@
         </is>
       </c>
       <c r="B256">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C256">
         <v>36203</v>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="B257">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C257">
         <v>42628</v>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="B258">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C258">
         <v>39467</v>
@@ -5785,7 +5785,7 @@
         </is>
       </c>
       <c r="B259">
-        <v>11.2</v>
+        <v>0.112</v>
       </c>
       <c r="C259">
         <v>39940</v>
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="B260">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C260">
         <v>34823</v>
@@ -5827,7 +5827,7 @@
         </is>
       </c>
       <c r="B261">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C261">
         <v>43870</v>
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="B262">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C262">
         <v>43645</v>
@@ -5869,7 +5869,7 @@
         </is>
       </c>
       <c r="B263">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C263">
         <v>36016</v>
@@ -5890,7 +5890,7 @@
         </is>
       </c>
       <c r="B264">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C264">
         <v>42509</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="B265">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C265">
         <v>33243</v>
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="B266">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C266">
         <v>35349</v>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="B267">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C267">
         <v>38771</v>
@@ -5974,7 +5974,7 @@
         </is>
       </c>
       <c r="B268">
-        <v>6.3</v>
+        <v>0.063</v>
       </c>
       <c r="C268">
         <v>48820</v>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="B269">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C269">
         <v>37726</v>
@@ -6016,7 +6016,7 @@
         </is>
       </c>
       <c r="B270">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C270">
         <v>37676</v>
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="B271">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C271">
         <v>36821</v>
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="B272">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C272">
         <v>33695</v>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="B273">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C273">
         <v>40278</v>
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="B274">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C274">
         <v>42236</v>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="B275">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C275">
         <v>52779</v>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="B276">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C276">
         <v>36680</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="B277">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C277">
         <v>35300</v>
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="B278">
-        <v>6.6</v>
+        <v>0.066</v>
       </c>
       <c r="C278">
         <v>43681</v>
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="B279">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C279">
         <v>39632</v>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="B280">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C280">
         <v>47003</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="B281">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C281">
         <v>43323</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="B282">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C282">
         <v>42058</v>
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="B283">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C283">
         <v>43059</v>
@@ -6310,7 +6310,7 @@
         </is>
       </c>
       <c r="B284">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C284">
         <v>45671</v>
@@ -6331,7 +6331,7 @@
         </is>
       </c>
       <c r="B285">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C285">
         <v>39640</v>
@@ -6352,7 +6352,7 @@
         </is>
       </c>
       <c r="B286">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C286">
         <v>36376</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="B287">
-        <v>5.8</v>
+        <v>0.058</v>
       </c>
       <c r="C287">
         <v>57515</v>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="B288">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C288">
         <v>45699</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="B289">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C289">
         <v>44709</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="B290">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C290">
         <v>38861</v>
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="B291">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C291">
         <v>41578</v>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="B292">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C292">
         <v>38690</v>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="B293">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C293">
         <v>41158</v>
@@ -6520,7 +6520,7 @@
         </is>
       </c>
       <c r="B294">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="C294">
         <v>34912</v>
@@ -6541,7 +6541,7 @@
         </is>
       </c>
       <c r="B295">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C295">
         <v>36061</v>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="B296">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C296">
         <v>52765</v>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="B297">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C297">
         <v>43059</v>
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="B298">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C298">
         <v>45798</v>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="B299">
-        <v>13.5</v>
+        <v>0.135</v>
       </c>
       <c r="C299">
         <v>35316</v>
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="B300">
-        <v>5.5</v>
+        <v>0.055</v>
       </c>
       <c r="C300">
         <v>49335</v>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="B301">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C301">
         <v>45333</v>
@@ -6688,7 +6688,7 @@
         </is>
       </c>
       <c r="B302">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C302">
         <v>39314</v>
@@ -6709,7 +6709,7 @@
         </is>
       </c>
       <c r="B303">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C303">
         <v>45186</v>
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="B304">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C304">
         <v>39239</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="B305">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C305">
         <v>46998</v>
@@ -6772,7 +6772,7 @@
         </is>
       </c>
       <c r="B306">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C306">
         <v>39479</v>
@@ -6793,7 +6793,7 @@
         </is>
       </c>
       <c r="B307">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C307">
         <v>43143</v>
@@ -6814,7 +6814,7 @@
         </is>
       </c>
       <c r="B308">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C308">
         <v>36703</v>
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="B309">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C309">
         <v>36463</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="B310">
-        <v>3.6</v>
+        <v>0.036</v>
       </c>
       <c r="C310">
         <v>80876</v>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="B311">
-        <v>4.9</v>
+        <v>0.049</v>
       </c>
       <c r="C311">
         <v>58942</v>
@@ -6898,7 +6898,7 @@
         </is>
       </c>
       <c r="B312">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C312">
         <v>45689</v>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="B313">
-        <v>4.6</v>
+        <v>0.046</v>
       </c>
       <c r="C313">
         <v>61595</v>
@@ -6940,7 +6940,7 @@
         </is>
       </c>
       <c r="B314">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C314">
         <v>40747</v>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="B315">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C315">
         <v>45952</v>
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="B316">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C316">
         <v>42351</v>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="B317">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C317">
         <v>41585</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="B318">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C318">
         <v>46027</v>
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="B319">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C319">
         <v>35885</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="B320">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C320">
         <v>39813</v>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="B321">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C321">
         <v>39551</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="B322">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C322">
         <v>54109</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="B323">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C323">
         <v>33392</v>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="B324">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C324">
         <v>47134</v>
@@ -7171,7 +7171,7 @@
         </is>
       </c>
       <c r="B325">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C325">
         <v>44458</v>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="B326">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C326">
         <v>39824</v>
@@ -7213,7 +7213,7 @@
         </is>
       </c>
       <c r="B327">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C327">
         <v>40193</v>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="B328">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C328">
         <v>38606</v>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="B329">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C329">
         <v>39539</v>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="B330">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C330">
         <v>41478</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="B331">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C331">
         <v>43051</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="B332">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C332">
         <v>38079</v>
@@ -7339,7 +7339,7 @@
         </is>
       </c>
       <c r="B333">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C333">
         <v>39553</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="B334">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C334">
         <v>35722</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="B335">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C335">
         <v>41444</v>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="B336">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C336">
         <v>49669</v>
@@ -7423,7 +7423,7 @@
         </is>
       </c>
       <c r="B337">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C337">
         <v>40916</v>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
       <c r="B338">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C338">
         <v>43217</v>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="B339">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C339">
         <v>41587</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="B340">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C340">
         <v>32784</v>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="B341">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C341">
         <v>37368</v>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="B342">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C342">
         <v>36370</v>
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="B343">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C343">
         <v>38643</v>
@@ -7570,7 +7570,7 @@
         </is>
       </c>
       <c r="B344">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C344">
         <v>37860</v>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="B345">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C345">
         <v>54803</v>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="B346">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C346">
         <v>48980</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="B347">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C347">
         <v>37066</v>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="B348">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C348">
         <v>41313</v>
@@ -7675,7 +7675,7 @@
         </is>
       </c>
       <c r="B349">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C349">
         <v>36925</v>
@@ -7696,7 +7696,7 @@
         </is>
       </c>
       <c r="B350">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C350">
         <v>43657</v>
@@ -7717,7 +7717,7 @@
         </is>
       </c>
       <c r="B351">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C351">
         <v>40186</v>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="B352">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C352">
         <v>40350</v>
@@ -7759,7 +7759,7 @@
         </is>
       </c>
       <c r="B353">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C353">
         <v>35901</v>
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="B354">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C354">
         <v>44255</v>
@@ -7801,7 +7801,7 @@
         </is>
       </c>
       <c r="B355">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C355">
         <v>44550</v>
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="B356">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C356">
         <v>36871</v>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="B357">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C357">
         <v>42029</v>
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="B358">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C358">
         <v>34374</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="B359">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C359">
         <v>36589</v>
@@ -7906,7 +7906,7 @@
         </is>
       </c>
       <c r="B360">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C360">
         <v>39607</v>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="B361">
-        <v>6.7</v>
+        <v>0.067</v>
       </c>
       <c r="C361">
         <v>49753</v>
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="B362">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C362">
         <v>39035</v>
@@ -7969,7 +7969,7 @@
         </is>
       </c>
       <c r="B363">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C363">
         <v>38360</v>
@@ -7990,7 +7990,7 @@
         </is>
       </c>
       <c r="B364">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C364">
         <v>38282</v>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="B365">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C365">
         <v>34630</v>
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="B366">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C366">
         <v>40647</v>
@@ -8053,7 +8053,7 @@
         </is>
       </c>
       <c r="B367">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C367">
         <v>43404</v>
@@ -8074,7 +8074,7 @@
         </is>
       </c>
       <c r="B368">
-        <v>5.8</v>
+        <v>0.058</v>
       </c>
       <c r="C368">
         <v>53901</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="B369">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C369">
         <v>37427</v>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="B370">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C370">
         <v>35911</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="B371">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C371">
         <v>44382</v>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="B372">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C372">
         <v>39566</v>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="B373">
-        <v>6.2</v>
+        <v>0.062</v>
       </c>
       <c r="C373">
         <v>47499</v>
@@ -8200,7 +8200,7 @@
         </is>
       </c>
       <c r="B374">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C374">
         <v>43217</v>
@@ -8221,7 +8221,7 @@
         </is>
       </c>
       <c r="B375">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C375">
         <v>43781</v>
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="B376">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C376">
         <v>42867</v>
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="B377">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C377">
         <v>47091</v>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="B378">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C378">
         <v>41414</v>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="B379">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C379">
         <v>36551</v>
@@ -8326,7 +8326,7 @@
         </is>
       </c>
       <c r="B380">
-        <v>6</v>
+        <v>0.06</v>
       </c>
       <c r="C380">
         <v>59206</v>
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="B381">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C381">
         <v>46143</v>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="B382">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C382">
         <v>45231</v>
@@ -8389,7 +8389,7 @@
         </is>
       </c>
       <c r="B383">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C383">
         <v>39593</v>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="B384">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C384">
         <v>42904</v>
@@ -8431,7 +8431,7 @@
         </is>
       </c>
       <c r="B385">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C385">
         <v>40120</v>
@@ -8452,7 +8452,7 @@
         </is>
       </c>
       <c r="B386">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C386">
         <v>42951</v>
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="B387">
-        <v>14.3</v>
+        <v>0.143</v>
       </c>
       <c r="C387">
         <v>35581</v>
@@ -8494,7 +8494,7 @@
         </is>
       </c>
       <c r="B388">
-        <v>13.1</v>
+        <v>0.131</v>
       </c>
       <c r="C388">
         <v>37456</v>
@@ -8515,7 +8515,7 @@
         </is>
       </c>
       <c r="B389">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C389">
         <v>54101</v>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="B390">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C390">
         <v>44130</v>
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="B391">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C391">
         <v>46930</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="B392">
-        <v>15.3</v>
+        <v>0.153</v>
       </c>
       <c r="C392">
         <v>35843</v>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="B393">
-        <v>6.2</v>
+        <v>0.062</v>
       </c>
       <c r="C393">
         <v>50215</v>
@@ -8620,7 +8620,7 @@
         </is>
       </c>
       <c r="B394">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C394">
         <v>46897</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B395">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C395">
         <v>39393</v>
@@ -8662,7 +8662,7 @@
         </is>
       </c>
       <c r="B396">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C396">
         <v>47243</v>
@@ -8683,7 +8683,7 @@
         </is>
       </c>
       <c r="B397">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C397">
         <v>40879</v>
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="B398">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C398">
         <v>47515</v>
@@ -8725,7 +8725,7 @@
         </is>
       </c>
       <c r="B399">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C399">
         <v>40815</v>
@@ -8746,7 +8746,7 @@
         </is>
       </c>
       <c r="B400">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C400">
         <v>44752</v>
@@ -8767,7 +8767,7 @@
         </is>
       </c>
       <c r="B401">
-        <v>13.7</v>
+        <v>0.137</v>
       </c>
       <c r="C401">
         <v>37195</v>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="B402">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C402">
         <v>37849</v>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="B403">
-        <v>3.9</v>
+        <v>0.039</v>
       </c>
       <c r="C403">
         <v>82196</v>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="B404">
-        <v>5.4</v>
+        <v>0.05400000000000001</v>
       </c>
       <c r="C404">
         <v>62657</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="B405">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C405">
         <v>46893</v>
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="B406">
-        <v>5.2</v>
+        <v>0.052</v>
       </c>
       <c r="C406">
         <v>63058</v>
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="B407">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C407">
         <v>41157</v>
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="B408">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C408">
         <v>45588</v>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="B409">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C409">
         <v>43165</v>
@@ -8956,7 +8956,7 @@
         </is>
       </c>
       <c r="B410">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C410">
         <v>43134</v>
@@ -8977,7 +8977,7 @@
         </is>
       </c>
       <c r="B411">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C411">
         <v>47557</v>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="B412">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C412">
         <v>38167</v>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="B413">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C413">
         <v>40906</v>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="B414">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C414">
         <v>41330</v>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="B415">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C415">
         <v>55594</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="B416">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C416">
         <v>34668</v>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="B417">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C417">
         <v>48998</v>
@@ -9124,7 +9124,7 @@
         </is>
       </c>
       <c r="B418">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C418">
         <v>46841</v>
@@ -9145,7 +9145,7 @@
         </is>
       </c>
       <c r="B419">
-        <v>14.8</v>
+        <v>0.148</v>
       </c>
       <c r="C419">
         <v>40894</v>
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="B420">
-        <v>11.2</v>
+        <v>0.112</v>
       </c>
       <c r="C420">
         <v>41906</v>
@@ -9187,7 +9187,7 @@
         </is>
       </c>
       <c r="B421">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C421">
         <v>39297</v>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="B422">
-        <v>12.1</v>
+        <v>0.121</v>
       </c>
       <c r="C422">
         <v>40480</v>
@@ -9229,7 +9229,7 @@
         </is>
       </c>
       <c r="B423">
-        <v>14.1</v>
+        <v>0.141</v>
       </c>
       <c r="C423">
         <v>42702</v>
@@ -9250,7 +9250,7 @@
         </is>
       </c>
       <c r="B424">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C424">
         <v>45040</v>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="B425">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C425">
         <v>39421</v>
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="B426">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C426">
         <v>41280</v>
@@ -9313,7 +9313,7 @@
         </is>
       </c>
       <c r="B427">
-        <v>14</v>
+        <v>0.14</v>
       </c>
       <c r="C427">
         <v>36224</v>
@@ -9334,7 +9334,7 @@
         </is>
       </c>
       <c r="B428">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C428">
         <v>43486</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="B429">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C429">
         <v>51378</v>
@@ -9376,7 +9376,7 @@
         </is>
       </c>
       <c r="B430">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C430">
         <v>43726</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="B431">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C431">
         <v>44255</v>
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="B432">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C432">
         <v>43448</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B433">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C433">
         <v>33684</v>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="B434">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C434">
         <v>38589</v>
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="B435">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C435">
         <v>37467</v>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="B436">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C436">
         <v>39472</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B437">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C437">
         <v>39972</v>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="B438">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C438">
         <v>56935</v>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="B439">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C439">
         <v>50765</v>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="B440">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C440">
         <v>39066</v>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="B441">
-        <v>9.9</v>
+        <v>0.099</v>
       </c>
       <c r="C441">
         <v>42273</v>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="B442">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C442">
         <v>37877</v>
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="B443">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C443">
         <v>45555</v>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="B444">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C444">
         <v>42623</v>
@@ -9691,7 +9691,7 @@
         </is>
       </c>
       <c r="B445">
-        <v>13.5</v>
+        <v>0.135</v>
       </c>
       <c r="C445">
         <v>41365</v>
@@ -9712,7 +9712,7 @@
         </is>
       </c>
       <c r="B446">
-        <v>13.4</v>
+        <v>0.134</v>
       </c>
       <c r="C446">
         <v>37193</v>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="B447">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C447">
         <v>45910</v>
@@ -9754,7 +9754,7 @@
         </is>
       </c>
       <c r="B448">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C448">
         <v>46831</v>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="B449">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C449">
         <v>38913</v>
@@ -9796,7 +9796,7 @@
         </is>
       </c>
       <c r="B450">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C450">
         <v>43032</v>
@@ -9817,7 +9817,7 @@
         </is>
       </c>
       <c r="B451">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="C451">
         <v>35882</v>
@@ -9838,7 +9838,7 @@
         </is>
       </c>
       <c r="B452">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C452">
         <v>38502</v>
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="B453">
-        <v>13.4</v>
+        <v>0.134</v>
       </c>
       <c r="C453">
         <v>40036</v>
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="B454">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C454">
         <v>51512</v>
@@ -9901,7 +9901,7 @@
         </is>
       </c>
       <c r="B455">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C455">
         <v>41569</v>
@@ -9922,7 +9922,7 @@
         </is>
       </c>
       <c r="B456">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C456">
         <v>39117</v>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B457">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C457">
         <v>39545</v>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="B458">
-        <v>15.4</v>
+        <v>0.154</v>
       </c>
       <c r="C458">
         <v>35736</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B459">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C459">
         <v>42009</v>
@@ -10006,7 +10006,7 @@
         </is>
       </c>
       <c r="B460">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C460">
         <v>46477</v>
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B461">
-        <v>6.3</v>
+        <v>0.063</v>
       </c>
       <c r="C461">
         <v>55677</v>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="B462">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C462">
         <v>38787</v>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="B463">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C463">
         <v>36145</v>
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="B464">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C464">
         <v>45645</v>
@@ -10111,7 +10111,7 @@
         </is>
       </c>
       <c r="B465">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C465">
         <v>41890</v>
@@ -10132,7 +10132,7 @@
         </is>
       </c>
       <c r="B466">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C466">
         <v>47981</v>
@@ -10153,7 +10153,7 @@
         </is>
       </c>
       <c r="B467">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C467">
         <v>44051</v>
@@ -10174,7 +10174,7 @@
         </is>
       </c>
       <c r="B468">
-        <v>11.5</v>
+        <v>0.115</v>
       </c>
       <c r="C468">
         <v>45381</v>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="B469">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C469">
         <v>45506</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="B470">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C470">
         <v>46172</v>
@@ -10237,7 +10237,7 @@
         </is>
       </c>
       <c r="B471">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C471">
         <v>42467</v>
@@ -10258,7 +10258,7 @@
         </is>
       </c>
       <c r="B472">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C472">
         <v>37671</v>
@@ -10279,7 +10279,7 @@
         </is>
       </c>
       <c r="B473">
-        <v>5.6</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="C473">
         <v>60539</v>
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="B474">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C474">
         <v>47813</v>
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="B475">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C475">
         <v>45702</v>
@@ -10342,7 +10342,7 @@
         </is>
       </c>
       <c r="B476">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C476">
         <v>40999</v>
@@ -10363,7 +10363,7 @@
         </is>
       </c>
       <c r="B477">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C477">
         <v>43158</v>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="B478">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C478">
         <v>40196</v>
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="B479">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C479">
         <v>44979</v>
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="B480">
-        <v>17.5</v>
+        <v>0.175</v>
       </c>
       <c r="C480">
         <v>34739</v>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="B481">
-        <v>16.1</v>
+        <v>0.161</v>
       </c>
       <c r="C481">
         <v>37074</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="B482">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C482">
         <v>54468</v>
@@ -10489,7 +10489,7 @@
         </is>
       </c>
       <c r="B483">
-        <v>11.2</v>
+        <v>0.112</v>
       </c>
       <c r="C483">
         <v>44424</v>
@@ -10510,7 +10510,7 @@
         </is>
       </c>
       <c r="B484">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C484">
         <v>45109</v>
@@ -10531,7 +10531,7 @@
         </is>
       </c>
       <c r="B485">
-        <v>18.3</v>
+        <v>0.183</v>
       </c>
       <c r="C485">
         <v>35163</v>
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="B486">
-        <v>6.5</v>
+        <v>0.065</v>
       </c>
       <c r="C486">
         <v>51191</v>
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="B487">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C487">
         <v>45811</v>
@@ -10594,7 +10594,7 @@
         </is>
       </c>
       <c r="B488">
-        <v>13.7</v>
+        <v>0.137</v>
       </c>
       <c r="C488">
         <v>40714</v>
@@ -10615,7 +10615,7 @@
         </is>
       </c>
       <c r="B489">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C489">
         <v>48039</v>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="B490">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C490">
         <v>41832</v>
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="B491">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C491">
         <v>47711</v>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="B492">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C492">
         <v>41289</v>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="B493">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C493">
         <v>43371</v>
@@ -10720,7 +10720,7 @@
         </is>
       </c>
       <c r="B494">
-        <v>17.9</v>
+        <v>0.179</v>
       </c>
       <c r="C494">
         <v>36733</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="B495">
-        <v>15.1</v>
+        <v>0.151</v>
       </c>
       <c r="C495">
         <v>37441</v>
@@ -10762,7 +10762,7 @@
         </is>
       </c>
       <c r="B496">
-        <v>3.9</v>
+        <v>0.039</v>
       </c>
       <c r="C496">
         <v>79927</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B497">
-        <v>4.7</v>
+        <v>0.047</v>
       </c>
       <c r="C497">
         <v>60343</v>
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="B498">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C498">
         <v>46420</v>
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="B499">
-        <v>4.7</v>
+        <v>0.047</v>
       </c>
       <c r="C499">
         <v>59720</v>
@@ -10846,7 +10846,7 @@
         </is>
       </c>
       <c r="B500">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C500">
         <v>42698</v>
@@ -10867,7 +10867,7 @@
         </is>
       </c>
       <c r="B501">
-        <v>12.8</v>
+        <v>0.128</v>
       </c>
       <c r="C501">
         <v>45725</v>
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="B502">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C502">
         <v>43945</v>
@@ -10909,7 +10909,7 @@
         </is>
       </c>
       <c r="B503">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C503">
         <v>40939</v>
@@ -10930,7 +10930,7 @@
         </is>
       </c>
       <c r="B504">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C504">
         <v>48016</v>
@@ -10951,7 +10951,7 @@
         </is>
       </c>
       <c r="B505">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C505">
         <v>33813</v>
@@ -10972,7 +10972,7 @@
         </is>
       </c>
       <c r="B506">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C506">
         <v>39527</v>
@@ -10993,7 +10993,7 @@
         </is>
       </c>
       <c r="B507">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C507">
         <v>42735</v>
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="B508">
-        <v>7.1</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C508">
         <v>56854</v>
@@ -11035,7 +11035,7 @@
         </is>
       </c>
       <c r="B509">
-        <v>17.6</v>
+        <v>0.176</v>
       </c>
       <c r="C509">
         <v>38175</v>
@@ -11056,7 +11056,7 @@
         </is>
       </c>
       <c r="B510">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C510">
         <v>47567</v>
@@ -11077,7 +11077,7 @@
         </is>
       </c>
       <c r="B511">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C511">
         <v>48857</v>
@@ -11098,7 +11098,7 @@
         </is>
       </c>
       <c r="B512">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C512">
         <v>42917</v>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="B513">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C513">
         <v>45537</v>
@@ -11140,7 +11140,7 @@
         </is>
       </c>
       <c r="B514">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C514">
         <v>40009</v>
@@ -11161,7 +11161,7 @@
         </is>
       </c>
       <c r="B515">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C515">
         <v>40747</v>
@@ -11182,7 +11182,7 @@
         </is>
       </c>
       <c r="B516">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C516">
         <v>42129</v>
@@ -11203,7 +11203,7 @@
         </is>
       </c>
       <c r="B517">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C517">
         <v>46990</v>
@@ -11224,7 +11224,7 @@
         </is>
       </c>
       <c r="B518">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C518">
         <v>40303</v>
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="B519">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C519">
         <v>40967</v>
@@ -11266,7 +11266,7 @@
         </is>
       </c>
       <c r="B520">
-        <v>22.2</v>
+        <v>0.222</v>
       </c>
       <c r="C520">
         <v>35728</v>
@@ -11287,7 +11287,7 @@
         </is>
       </c>
       <c r="B521">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C521">
         <v>44177</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="B522">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C522">
         <v>51329</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B523">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C523">
         <v>46739</v>
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="B524">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C524">
         <v>48445</v>
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B525">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C525">
         <v>43969</v>
@@ -11392,7 +11392,7 @@
         </is>
       </c>
       <c r="B526">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C526">
         <v>33691</v>
@@ -11413,7 +11413,7 @@
         </is>
       </c>
       <c r="B527">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C527">
         <v>38958</v>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="B528">
-        <v>15.4</v>
+        <v>0.154</v>
       </c>
       <c r="C528">
         <v>38240</v>
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="B529">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C529">
         <v>39472</v>
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="B530">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C530">
         <v>38496</v>
@@ -11497,7 +11497,7 @@
         </is>
       </c>
       <c r="B531">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C531">
         <v>56496</v>
@@ -11518,7 +11518,7 @@
         </is>
       </c>
       <c r="B532">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C532">
         <v>52740</v>
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="B533">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C533">
         <v>41106</v>
@@ -11560,7 +11560,7 @@
         </is>
       </c>
       <c r="B534">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C534">
         <v>43760</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="B535">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C535">
         <v>38805</v>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="B536">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C536">
         <v>45822</v>
@@ -11623,7 +11623,7 @@
         </is>
       </c>
       <c r="B537">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C537">
         <v>43755</v>
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="B538">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C538">
         <v>41565</v>
@@ -11665,7 +11665,7 @@
         </is>
       </c>
       <c r="B539">
-        <v>14.9</v>
+        <v>0.149</v>
       </c>
       <c r="C539">
         <v>36156</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="B540">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C540">
         <v>47161</v>
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="B541">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C541">
         <v>45208</v>
@@ -11728,7 +11728,7 @@
         </is>
       </c>
       <c r="B542">
-        <v>14.5</v>
+        <v>0.145</v>
       </c>
       <c r="C542">
         <v>39745</v>
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="B543">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C543">
         <v>44209</v>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B544">
-        <v>14.3</v>
+        <v>0.143</v>
       </c>
       <c r="C544">
         <v>37254</v>
@@ -11791,7 +11791,7 @@
         </is>
       </c>
       <c r="B545">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C545">
         <v>39750</v>
@@ -11812,7 +11812,7 @@
         </is>
       </c>
       <c r="B546">
-        <v>17.9</v>
+        <v>0.179</v>
       </c>
       <c r="C546">
         <v>40721</v>
@@ -11833,7 +11833,7 @@
         </is>
       </c>
       <c r="B547">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C547">
         <v>51808</v>
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="B548">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C548">
         <v>45307</v>
@@ -11875,7 +11875,7 @@
         </is>
       </c>
       <c r="B549">
-        <v>13.4</v>
+        <v>0.134</v>
       </c>
       <c r="C549">
         <v>41464</v>
@@ -11896,7 +11896,7 @@
         </is>
       </c>
       <c r="B550">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C550">
         <v>40117</v>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="B551">
-        <v>17.4</v>
+        <v>0.174</v>
       </c>
       <c r="C551">
         <v>35763</v>
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="B552">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C552">
         <v>42705</v>
@@ -11959,7 +11959,7 @@
         </is>
       </c>
       <c r="B553">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C553">
         <v>47674</v>
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="B554">
-        <v>6.3</v>
+        <v>0.063</v>
       </c>
       <c r="C554">
         <v>54475</v>
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="B555">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C555">
         <v>38005</v>
@@ -12022,7 +12022,7 @@
         </is>
       </c>
       <c r="B556">
-        <v>14.4</v>
+        <v>0.144</v>
       </c>
       <c r="C556">
         <v>35557</v>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="B557">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C557">
         <v>45822</v>
@@ -12064,7 +12064,7 @@
         </is>
       </c>
       <c r="B558">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C558">
         <v>42877</v>
@@ -12085,7 +12085,7 @@
         </is>
       </c>
       <c r="B559">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C559">
         <v>47709</v>
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="B560">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C560">
         <v>45414</v>
@@ -12127,7 +12127,7 @@
         </is>
       </c>
       <c r="B561">
-        <v>13.5</v>
+        <v>0.135</v>
       </c>
       <c r="C561">
         <v>41976</v>
@@ -12148,7 +12148,7 @@
         </is>
       </c>
       <c r="B562">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C562">
         <v>45844</v>
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="B563">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C563">
         <v>49681</v>
@@ -12190,7 +12190,7 @@
         </is>
       </c>
       <c r="B564">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C564">
         <v>43645</v>
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="B565">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="C565">
         <v>38185</v>
@@ -12232,7 +12232,7 @@
         </is>
       </c>
       <c r="B566">
-        <v>6</v>
+        <v>0.06</v>
       </c>
       <c r="C566">
         <v>63619</v>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="B567">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C567">
         <v>49151</v>
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="B568">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C568">
         <v>45092</v>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="B569">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C569">
         <v>41701</v>
@@ -12316,7 +12316,7 @@
         </is>
       </c>
       <c r="B570">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C570">
         <v>42662</v>
@@ -12337,7 +12337,7 @@
         </is>
       </c>
       <c r="B571">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C571">
         <v>40860</v>
@@ -12358,7 +12358,7 @@
         </is>
       </c>
       <c r="B572">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C572">
         <v>44485</v>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="B573">
-        <v>17.6</v>
+        <v>0.176</v>
       </c>
       <c r="C573">
         <v>37240</v>
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="B574">
-        <v>14.5</v>
+        <v>0.145</v>
       </c>
       <c r="C574">
         <v>39276</v>
@@ -12421,7 +12421,7 @@
         </is>
       </c>
       <c r="B575">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C575">
         <v>55086</v>
@@ -12442,7 +12442,7 @@
         </is>
       </c>
       <c r="B576">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C576">
         <v>44962</v>
@@ -12463,7 +12463,7 @@
         </is>
       </c>
       <c r="B577">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C577">
         <v>46561</v>
@@ -12484,7 +12484,7 @@
         </is>
       </c>
       <c r="B578">
-        <v>19.8</v>
+        <v>0.198</v>
       </c>
       <c r="C578">
         <v>35698</v>
@@ -12505,7 +12505,7 @@
         </is>
       </c>
       <c r="B579">
-        <v>6.8</v>
+        <v>0.068</v>
       </c>
       <c r="C579">
         <v>49399</v>
@@ -12526,7 +12526,7 @@
         </is>
       </c>
       <c r="B580">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C580">
         <v>47309</v>
@@ -12547,7 +12547,7 @@
         </is>
       </c>
       <c r="B581">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C581">
         <v>40957</v>
@@ -12568,7 +12568,7 @@
         </is>
       </c>
       <c r="B582">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C582">
         <v>50733</v>
@@ -12589,7 +12589,7 @@
         </is>
       </c>
       <c r="B583">
-        <v>11.2</v>
+        <v>0.112</v>
       </c>
       <c r="C583">
         <v>41768</v>
@@ -12610,7 +12610,7 @@
         </is>
       </c>
       <c r="B584">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C584">
         <v>49430</v>
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="B585">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C585">
         <v>38956</v>
@@ -12652,7 +12652,7 @@
         </is>
       </c>
       <c r="B586">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C586">
         <v>44010</v>
@@ -12673,7 +12673,7 @@
         </is>
       </c>
       <c r="B587">
-        <v>15.6</v>
+        <v>0.156</v>
       </c>
       <c r="C587">
         <v>38939</v>
@@ -12694,7 +12694,7 @@
         </is>
       </c>
       <c r="B588">
-        <v>16.1</v>
+        <v>0.161</v>
       </c>
       <c r="C588">
         <v>36480</v>
@@ -12715,7 +12715,7 @@
         </is>
       </c>
       <c r="B589">
-        <v>3.9</v>
+        <v>0.039</v>
       </c>
       <c r="C589">
         <v>76891</v>
@@ -12736,7 +12736,7 @@
         </is>
       </c>
       <c r="B590">
-        <v>5.8</v>
+        <v>0.058</v>
       </c>
       <c r="C590">
         <v>62442</v>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="B591">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C591">
         <v>49196</v>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="B592">
-        <v>5.6</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="C592">
         <v>62312</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="B593">
-        <v>11.5</v>
+        <v>0.115</v>
       </c>
       <c r="C593">
         <v>41459</v>
@@ -12820,7 +12820,7 @@
         </is>
       </c>
       <c r="B594">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C594">
         <v>44964</v>
@@ -12841,7 +12841,7 @@
         </is>
       </c>
       <c r="B595">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C595">
         <v>45289</v>
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="B596">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C596">
         <v>43050</v>
@@ -12883,7 +12883,7 @@
         </is>
       </c>
       <c r="B597">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C597">
         <v>50675</v>
@@ -12904,7 +12904,7 @@
         </is>
       </c>
       <c r="B598">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C598">
         <v>36489</v>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="B599">
-        <v>14.3</v>
+        <v>0.143</v>
       </c>
       <c r="C599">
         <v>41618</v>
@@ -12946,7 +12946,7 @@
         </is>
       </c>
       <c r="B600">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C600">
         <v>42822</v>
@@ -12967,7 +12967,7 @@
         </is>
       </c>
       <c r="B601">
-        <v>6.5</v>
+        <v>0.065</v>
       </c>
       <c r="C601">
         <v>60804</v>
@@ -12988,7 +12988,7 @@
         </is>
       </c>
       <c r="B602">
-        <v>19.7</v>
+        <v>0.197</v>
       </c>
       <c r="C602">
         <v>35722</v>
@@ -13009,7 +13009,7 @@
         </is>
       </c>
       <c r="B603">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C603">
         <v>48410</v>
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="B604">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C604">
         <v>48693</v>
@@ -13051,7 +13051,7 @@
         </is>
       </c>
       <c r="B605">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C605">
         <v>46389</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="B606">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C606">
         <v>46596</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="B607">
-        <v>12.1</v>
+        <v>0.121</v>
       </c>
       <c r="C607">
         <v>38101</v>
@@ -13114,7 +13114,7 @@
         </is>
       </c>
       <c r="B608">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C608">
         <v>41341</v>
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="B609">
-        <v>15.9</v>
+        <v>0.159</v>
       </c>
       <c r="C609">
         <v>42072</v>
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="B610">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C610">
         <v>50640</v>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="B611">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C611">
         <v>41787</v>
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="B612">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C612">
         <v>43129</v>
@@ -13219,7 +13219,7 @@
         </is>
       </c>
       <c r="B613">
-        <v>24.2</v>
+        <v>0.242</v>
       </c>
       <c r="C613">
         <v>38508</v>
@@ -13240,7 +13240,7 @@
         </is>
       </c>
       <c r="B614">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C614">
         <v>45454</v>
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="B615">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C615">
         <v>53515</v>
@@ -13282,7 +13282,7 @@
         </is>
       </c>
       <c r="B616">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C616">
         <v>48813</v>
@@ -13303,7 +13303,7 @@
         </is>
       </c>
       <c r="B617">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C617">
         <v>45196</v>
@@ -13324,7 +13324,7 @@
         </is>
       </c>
       <c r="B618">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C618">
         <v>46416</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="B619">
-        <v>16.8</v>
+        <v>0.168</v>
       </c>
       <c r="C619">
         <v>34489</v>
@@ -13366,7 +13366,7 @@
         </is>
       </c>
       <c r="B620">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C620">
         <v>41414</v>
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="B621">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C621">
         <v>39916</v>
@@ -13408,7 +13408,7 @@
         </is>
       </c>
       <c r="B622">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C622">
         <v>41426</v>
@@ -13429,7 +13429,7 @@
         </is>
       </c>
       <c r="B623">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C623">
         <v>40996</v>
@@ -13450,7 +13450,7 @@
         </is>
       </c>
       <c r="B624">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C624">
         <v>58176</v>
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="B625">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C625">
         <v>57018</v>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B626">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C626">
         <v>41275</v>
@@ -13513,7 +13513,7 @@
         </is>
       </c>
       <c r="B627">
-        <v>9.9</v>
+        <v>0.099</v>
       </c>
       <c r="C627">
         <v>44339</v>
@@ -13534,7 +13534,7 @@
         </is>
       </c>
       <c r="B628">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C628">
         <v>38143</v>
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="B629">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C629">
         <v>46275</v>
@@ -13576,7 +13576,7 @@
         </is>
       </c>
       <c r="B630">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C630">
         <v>44326</v>
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="B631">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C631">
         <v>44053</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="B632">
-        <v>14.9</v>
+        <v>0.149</v>
       </c>
       <c r="C632">
         <v>38422</v>
@@ -13639,7 +13639,7 @@
         </is>
       </c>
       <c r="B633">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C633">
         <v>50647</v>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="B634">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C634">
         <v>48529</v>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="B635">
-        <v>14</v>
+        <v>0.14</v>
       </c>
       <c r="C635">
         <v>40511</v>
@@ -13702,7 +13702,7 @@
         </is>
       </c>
       <c r="B636">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C636">
         <v>47351</v>
@@ -13723,7 +13723,7 @@
         </is>
       </c>
       <c r="B637">
-        <v>14.5</v>
+        <v>0.145</v>
       </c>
       <c r="C637">
         <v>39647</v>
@@ -13744,7 +13744,7 @@
         </is>
       </c>
       <c r="B638">
-        <v>14.5</v>
+        <v>0.145</v>
       </c>
       <c r="C638">
         <v>42316</v>
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="B639">
-        <v>17</v>
+        <v>0.17</v>
       </c>
       <c r="C639">
         <v>40618</v>
@@ -13786,7 +13786,7 @@
         </is>
       </c>
       <c r="B640">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C640">
         <v>51684</v>
@@ -13807,7 +13807,7 @@
         </is>
       </c>
       <c r="B641">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C641">
         <v>42998</v>
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="B642">
-        <v>14.6</v>
+        <v>0.146</v>
       </c>
       <c r="C642">
         <v>39963</v>
@@ -13849,7 +13849,7 @@
         </is>
       </c>
       <c r="B643">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C643">
         <v>40011</v>
@@ -13870,7 +13870,7 @@
         </is>
       </c>
       <c r="B644">
-        <v>21.5</v>
+        <v>0.215</v>
       </c>
       <c r="C644">
         <v>35686</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="B645">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C645">
         <v>43664</v>
@@ -13912,7 +13912,7 @@
         </is>
       </c>
       <c r="B646">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C646">
         <v>44431</v>
@@ -13933,7 +13933,7 @@
         </is>
       </c>
       <c r="B647">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C647">
         <v>61530</v>
@@ -13954,7 +13954,7 @@
         </is>
       </c>
       <c r="B648">
-        <v>15.7</v>
+        <v>0.157</v>
       </c>
       <c r="C648">
         <v>39521</v>
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="B649">
-        <v>14.2</v>
+        <v>0.142</v>
       </c>
       <c r="C649">
         <v>39105</v>
@@ -13996,7 +13996,7 @@
         </is>
       </c>
       <c r="B650">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C650">
         <v>48819</v>
@@ -14017,7 +14017,7 @@
         </is>
       </c>
       <c r="B651">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C651">
         <v>40188</v>
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="B652">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C652">
         <v>51228</v>
@@ -14059,7 +14059,7 @@
         </is>
       </c>
       <c r="B653">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C653">
         <v>47422</v>
@@ -14080,7 +14080,7 @@
         </is>
       </c>
       <c r="B654">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C654">
         <v>46601</v>
@@ -14101,7 +14101,7 @@
         </is>
       </c>
       <c r="B655">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C655">
         <v>47947</v>
@@ -14122,7 +14122,7 @@
         </is>
       </c>
       <c r="B656">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C656">
         <v>53395</v>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="B657">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C657">
         <v>44637</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="B658">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C658">
         <v>40996</v>
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="B659">
-        <v>6.6</v>
+        <v>0.066</v>
       </c>
       <c r="C659">
         <v>65106</v>
@@ -14206,7 +14206,7 @@
         </is>
       </c>
       <c r="B660">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C660">
         <v>52038</v>
@@ -14227,7 +14227,7 @@
         </is>
       </c>
       <c r="B661">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C661">
         <v>48013</v>
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="B662">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C662">
         <v>43794</v>
@@ -14269,7 +14269,7 @@
         </is>
       </c>
       <c r="B663">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C663">
         <v>45450</v>
@@ -14290,7 +14290,7 @@
         </is>
       </c>
       <c r="B664">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C664">
         <v>42755</v>
@@ -14311,7 +14311,7 @@
         </is>
       </c>
       <c r="B665">
-        <v>11.2</v>
+        <v>0.112</v>
       </c>
       <c r="C665">
         <v>46258</v>
@@ -14332,7 +14332,7 @@
         </is>
       </c>
       <c r="B666">
-        <v>16.6</v>
+        <v>0.166</v>
       </c>
       <c r="C666">
         <v>37942</v>
@@ -14353,7 +14353,7 @@
         </is>
       </c>
       <c r="B667">
-        <v>15</v>
+        <v>0.15</v>
       </c>
       <c r="C667">
         <v>41174</v>
@@ -14374,7 +14374,7 @@
         </is>
       </c>
       <c r="B668">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C668">
         <v>56660</v>
@@ -14395,7 +14395,7 @@
         </is>
       </c>
       <c r="B669">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C669">
         <v>45711</v>
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="B670">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C670">
         <v>49051</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="B671">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="C671">
         <v>38501</v>
@@ -14458,7 +14458,7 @@
         </is>
       </c>
       <c r="B672">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C672">
         <v>54404</v>
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="B673">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C673">
         <v>49395</v>
@@ -14500,7 +14500,7 @@
         </is>
       </c>
       <c r="B674">
-        <v>14.2</v>
+        <v>0.142</v>
       </c>
       <c r="C674">
         <v>39948</v>
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="B675">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C675">
         <v>52734</v>
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="B676">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C676">
         <v>42847</v>
@@ -14563,7 +14563,7 @@
         </is>
       </c>
       <c r="B677">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C677">
         <v>51541</v>
@@ -14584,7 +14584,7 @@
         </is>
       </c>
       <c r="B678">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C678">
         <v>45944</v>
@@ -14605,7 +14605,7 @@
         </is>
       </c>
       <c r="B679">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C679">
         <v>47197</v>
@@ -14626,7 +14626,7 @@
         </is>
       </c>
       <c r="B680">
-        <v>17.4</v>
+        <v>0.174</v>
       </c>
       <c r="C680">
         <v>37131</v>
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="B681">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C681">
         <v>41419</v>
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="B682">
-        <v>3.9</v>
+        <v>0.039</v>
       </c>
       <c r="C682">
         <v>83059</v>
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="B683">
-        <v>4.8</v>
+        <v>0.048</v>
       </c>
       <c r="C683">
         <v>65421</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="B684">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C684">
         <v>50418</v>
@@ -14731,7 +14731,7 @@
         </is>
       </c>
       <c r="B685">
-        <v>5</v>
+        <v>0.05</v>
       </c>
       <c r="C685">
         <v>66432</v>
@@ -14752,7 +14752,7 @@
         </is>
       </c>
       <c r="B686">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C686">
         <v>42306</v>
@@ -14773,7 +14773,7 @@
         </is>
       </c>
       <c r="B687">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="C687">
         <v>45569</v>
@@ -14794,7 +14794,7 @@
         </is>
       </c>
       <c r="B688">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C688">
         <v>46756</v>
@@ -14815,7 +14815,7 @@
         </is>
       </c>
       <c r="B689">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C689">
         <v>44935</v>
@@ -14836,7 +14836,7 @@
         </is>
       </c>
       <c r="B690">
-        <v>8.199999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="C690">
         <v>49945</v>
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B691">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C691">
         <v>40623</v>
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="B692">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C692">
         <v>45106</v>
@@ -14899,7 +14899,7 @@
         </is>
       </c>
       <c r="B693">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C693">
         <v>42634</v>
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="B694">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C694">
         <v>60381</v>
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="B695">
-        <v>17.1</v>
+        <v>0.171</v>
       </c>
       <c r="C695">
         <v>40042</v>
@@ -14962,7 +14962,7 @@
         </is>
       </c>
       <c r="B696">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C696">
         <v>50815</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="B697">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C697">
         <v>50487</v>
@@ -15004,7 +15004,7 @@
         </is>
       </c>
       <c r="B698">
-        <v>15</v>
+        <v>0.15</v>
       </c>
       <c r="C698">
         <v>47998</v>
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="B699">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C699">
         <v>44620</v>
@@ -15046,7 +15046,7 @@
         </is>
       </c>
       <c r="B700">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C700">
         <v>42018</v>
@@ -15067,7 +15067,7 @@
         </is>
       </c>
       <c r="B701">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C701">
         <v>43094</v>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="B702">
-        <v>15.6</v>
+        <v>0.156</v>
       </c>
       <c r="C702">
         <v>45160</v>
@@ -15109,7 +15109,7 @@
         </is>
       </c>
       <c r="B703">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C703">
         <v>50647</v>
@@ -15130,7 +15130,7 @@
         </is>
       </c>
       <c r="B704">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C704">
         <v>43574</v>
@@ -15151,7 +15151,7 @@
         </is>
       </c>
       <c r="B705">
-        <v>12.1</v>
+        <v>0.121</v>
       </c>
       <c r="C705">
         <v>44636</v>
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="B706">
-        <v>26</v>
+        <v>0.26</v>
       </c>
       <c r="C706">
         <v>39563</v>
@@ -15193,7 +15193,7 @@
         </is>
       </c>
       <c r="B707">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C707">
         <v>48453</v>
@@ -15214,7 +15214,7 @@
         </is>
       </c>
       <c r="B708">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C708">
         <v>53617</v>
@@ -15235,7 +15235,7 @@
         </is>
       </c>
       <c r="B709">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C709">
         <v>45107</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="B710">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C710">
         <v>46924</v>
@@ -15277,7 +15277,7 @@
         </is>
       </c>
       <c r="B711">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C711">
         <v>48099</v>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="B712">
-        <v>14.2</v>
+        <v>0.142</v>
       </c>
       <c r="C712">
         <v>38036</v>
@@ -15319,7 +15319,7 @@
         </is>
       </c>
       <c r="B713">
-        <v>13.1</v>
+        <v>0.131</v>
       </c>
       <c r="C713">
         <v>42291</v>
@@ -15340,7 +15340,7 @@
         </is>
       </c>
       <c r="B714">
-        <v>16.6</v>
+        <v>0.166</v>
       </c>
       <c r="C714">
         <v>37932</v>
@@ -15361,7 +15361,7 @@
         </is>
       </c>
       <c r="B715">
-        <v>12.1</v>
+        <v>0.121</v>
       </c>
       <c r="C715">
         <v>42711</v>
@@ -15382,7 +15382,7 @@
         </is>
       </c>
       <c r="B716">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C716">
         <v>38325</v>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="B717">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C717">
         <v>59992</v>
@@ -15424,7 +15424,7 @@
         </is>
       </c>
       <c r="B718">
-        <v>7.8</v>
+        <v>0.078</v>
       </c>
       <c r="C718">
         <v>55562</v>
@@ -15445,7 +15445,7 @@
         </is>
       </c>
       <c r="B719">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C719">
         <v>42651</v>
@@ -15466,7 +15466,7 @@
         </is>
       </c>
       <c r="B720">
-        <v>11.5</v>
+        <v>0.115</v>
       </c>
       <c r="C720">
         <v>48290</v>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="B721">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C721">
         <v>40071</v>
@@ -15508,7 +15508,7 @@
         </is>
       </c>
       <c r="B722">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C722">
         <v>49651</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="B723">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C723">
         <v>45246</v>
@@ -15550,7 +15550,7 @@
         </is>
       </c>
       <c r="B724">
-        <v>13.4</v>
+        <v>0.134</v>
       </c>
       <c r="C724">
         <v>44706</v>
@@ -15571,7 +15571,7 @@
         </is>
       </c>
       <c r="B725">
-        <v>16.5</v>
+        <v>0.165</v>
       </c>
       <c r="C725">
         <v>39451</v>
@@ -15592,7 +15592,7 @@
         </is>
       </c>
       <c r="B726">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C726">
         <v>48708</v>
@@ -15613,7 +15613,7 @@
         </is>
       </c>
       <c r="B727">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C727">
         <v>52269</v>
@@ -15634,7 +15634,7 @@
         </is>
       </c>
       <c r="B728">
-        <v>14.6</v>
+        <v>0.146</v>
       </c>
       <c r="C728">
         <v>40838</v>
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="B729">
-        <v>11.6</v>
+        <v>0.116</v>
       </c>
       <c r="C729">
         <v>46628</v>
@@ -15676,7 +15676,7 @@
         </is>
       </c>
       <c r="B730">
-        <v>13.7</v>
+        <v>0.137</v>
       </c>
       <c r="C730">
         <v>40957</v>
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="B731">
-        <v>14.4</v>
+        <v>0.144</v>
       </c>
       <c r="C731">
         <v>42987</v>
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="B732">
-        <v>19</v>
+        <v>0.19</v>
       </c>
       <c r="C732">
         <v>42325</v>
@@ -15739,7 +15739,7 @@
         </is>
       </c>
       <c r="B733">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C733">
         <v>54536</v>
@@ -15760,7 +15760,7 @@
         </is>
       </c>
       <c r="B734">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C734">
         <v>41103</v>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="B735">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C735">
         <v>42512</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="B736">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C736">
         <v>43637</v>
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="B737">
-        <v>16.9</v>
+        <v>0.169</v>
       </c>
       <c r="C737">
         <v>37381</v>
@@ -15844,7 +15844,7 @@
         </is>
       </c>
       <c r="B738">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C738">
         <v>45522</v>
@@ -15865,7 +15865,7 @@
         </is>
       </c>
       <c r="B739">
-        <v>8.300000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="C739">
         <v>49596</v>
@@ -15886,7 +15886,7 @@
         </is>
       </c>
       <c r="B740">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C740">
         <v>60748</v>
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="B741">
-        <v>14.7</v>
+        <v>0.147</v>
       </c>
       <c r="C741">
         <v>37288</v>
@@ -15928,7 +15928,7 @@
         </is>
       </c>
       <c r="B742">
-        <v>14.9</v>
+        <v>0.149</v>
       </c>
       <c r="C742">
         <v>39239</v>
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="B743">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C743">
         <v>45662</v>
@@ -15970,7 +15970,7 @@
         </is>
       </c>
       <c r="B744">
-        <v>9.4</v>
+        <v>0.094</v>
       </c>
       <c r="C744">
         <v>44881</v>
@@ -15991,7 +15991,7 @@
         </is>
       </c>
       <c r="B745">
-        <v>7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C745">
         <v>57903</v>
@@ -16012,7 +16012,7 @@
         </is>
       </c>
       <c r="B746">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C746">
         <v>48010</v>
@@ -16033,7 +16033,7 @@
         </is>
       </c>
       <c r="B747">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C747">
         <v>43304</v>
@@ -16054,7 +16054,7 @@
         </is>
       </c>
       <c r="B748">
-        <v>11.5</v>
+        <v>0.115</v>
       </c>
       <c r="C748">
         <v>49110</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="B749">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C749">
         <v>51850</v>
@@ -16096,7 +16096,7 @@
         </is>
       </c>
       <c r="B750">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C750">
         <v>46441</v>
@@ -16117,7 +16117,7 @@
         </is>
       </c>
       <c r="B751">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C751">
         <v>38769</v>
@@ -16138,7 +16138,7 @@
         </is>
       </c>
       <c r="B752">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C752">
         <v>72603</v>
@@ -16159,7 +16159,7 @@
         </is>
       </c>
       <c r="B753">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C753">
         <v>50082</v>
@@ -16180,7 +16180,7 @@
         </is>
       </c>
       <c r="B754">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C754">
         <v>50907</v>
@@ -16201,7 +16201,7 @@
         </is>
       </c>
       <c r="B755">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C755">
         <v>42778</v>
@@ -16222,7 +16222,7 @@
         </is>
       </c>
       <c r="B756">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C756">
         <v>48572</v>
@@ -16243,7 +16243,7 @@
         </is>
       </c>
       <c r="B757">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C757">
         <v>45768</v>
@@ -16264,7 +16264,7 @@
         </is>
       </c>
       <c r="B758">
-        <v>14.5</v>
+        <v>0.145</v>
       </c>
       <c r="C758">
         <v>46368</v>
@@ -16285,7 +16285,7 @@
         </is>
       </c>
       <c r="B759">
-        <v>17.1</v>
+        <v>0.171</v>
       </c>
       <c r="C759">
         <v>38653</v>
@@ -16306,7 +16306,7 @@
         </is>
       </c>
       <c r="B760">
-        <v>14.6</v>
+        <v>0.146</v>
       </c>
       <c r="C760">
         <v>43154</v>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="B761">
-        <v>8.1</v>
+        <v>0.081</v>
       </c>
       <c r="C761">
         <v>56434</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="B762">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C762">
         <v>49572</v>
@@ -16369,7 +16369,7 @@
         </is>
       </c>
       <c r="B763">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C763">
         <v>48698</v>
@@ -16390,7 +16390,7 @@
         </is>
       </c>
       <c r="B764">
-        <v>17.2</v>
+        <v>0.172</v>
       </c>
       <c r="C764">
         <v>39190</v>
@@ -16411,7 +16411,7 @@
         </is>
       </c>
       <c r="B765">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C765">
         <v>53779</v>
@@ -16432,7 +16432,7 @@
         </is>
       </c>
       <c r="B766">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C766">
         <v>49989</v>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="B767">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C767">
         <v>37548</v>
@@ -16474,7 +16474,7 @@
         </is>
       </c>
       <c r="B768">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C768">
         <v>50768</v>
@@ -16495,7 +16495,7 @@
         </is>
       </c>
       <c r="B769">
-        <v>11.5</v>
+        <v>0.115</v>
       </c>
       <c r="C769">
         <v>44377</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="B770">
-        <v>10.3</v>
+        <v>0.103</v>
       </c>
       <c r="C770">
         <v>51741</v>
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="B771">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C771">
         <v>45964</v>
@@ -16558,7 +16558,7 @@
         </is>
       </c>
       <c r="B772">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C772">
         <v>47795</v>
@@ -16579,7 +16579,7 @@
         </is>
       </c>
       <c r="B773">
-        <v>17.8</v>
+        <v>0.178</v>
       </c>
       <c r="C773">
         <v>38677</v>
@@ -16600,7 +16600,7 @@
         </is>
       </c>
       <c r="B774">
-        <v>13.7</v>
+        <v>0.137</v>
       </c>
       <c r="C774">
         <v>41378</v>
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="B775">
-        <v>4.2</v>
+        <v>0.042</v>
       </c>
       <c r="C775">
         <v>85829</v>
@@ -16642,7 +16642,7 @@
         </is>
       </c>
       <c r="B776">
-        <v>5.7</v>
+        <v>0.057</v>
       </c>
       <c r="C776">
         <v>64783</v>
@@ -16663,7 +16663,7 @@
         </is>
       </c>
       <c r="B777">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C777">
         <v>51964</v>
@@ -16684,7 +16684,7 @@
         </is>
       </c>
       <c r="B778">
-        <v>5.2</v>
+        <v>0.052</v>
       </c>
       <c r="C778">
         <v>67429</v>
@@ -16705,7 +16705,7 @@
         </is>
       </c>
       <c r="B779">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C779">
         <v>42416</v>
@@ -16726,7 +16726,7 @@
         </is>
       </c>
       <c r="B780">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C780">
         <v>49140</v>
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="B781">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C781">
         <v>46289</v>
@@ -16768,7 +16768,7 @@
         </is>
       </c>
       <c r="B782">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C782">
         <v>47428</v>
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="B783">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C783">
         <v>55706</v>
@@ -16810,7 +16810,7 @@
         </is>
       </c>
       <c r="B784">
-        <v>14.3</v>
+        <v>0.143</v>
       </c>
       <c r="C784">
         <v>41800</v>
@@ -16831,7 +16831,7 @@
         </is>
       </c>
       <c r="B785">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C785">
         <v>42646</v>
@@ -16852,7 +16852,7 @@
         </is>
       </c>
       <c r="B786">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C786">
         <v>43823</v>
@@ -16873,7 +16873,7 @@
         </is>
       </c>
       <c r="B787">
-        <v>7.4</v>
+        <v>0.07400000000000001</v>
       </c>
       <c r="C787">
         <v>62100</v>
@@ -16894,7 +16894,7 @@
         </is>
       </c>
       <c r="B788">
-        <v>16.6</v>
+        <v>0.166</v>
       </c>
       <c r="C788">
         <v>39509</v>
@@ -16915,7 +16915,7 @@
         </is>
       </c>
       <c r="B789">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C789">
         <v>50685</v>
@@ -16936,7 +16936,7 @@
         </is>
       </c>
       <c r="B790">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C790">
         <v>51160</v>
@@ -16957,7 +16957,7 @@
         </is>
       </c>
       <c r="B791">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C791">
         <v>50042</v>
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="B792">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C792">
         <v>46388</v>
@@ -16999,7 +16999,7 @@
         </is>
       </c>
       <c r="B793">
-        <v>14.3</v>
+        <v>0.143</v>
       </c>
       <c r="C793">
         <v>43165</v>
@@ -17020,7 +17020,7 @@
         </is>
       </c>
       <c r="B794">
-        <v>14.6</v>
+        <v>0.146</v>
       </c>
       <c r="C794">
         <v>44453</v>
@@ -17041,7 +17041,7 @@
         </is>
       </c>
       <c r="B795">
-        <v>16.5</v>
+        <v>0.165</v>
       </c>
       <c r="C795">
         <v>43823</v>
@@ -17062,7 +17062,7 @@
         </is>
       </c>
       <c r="B796">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C796">
         <v>50284</v>
@@ -17083,7 +17083,7 @@
         </is>
       </c>
       <c r="B797">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C797">
         <v>44900</v>
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="B798">
-        <v>14.2</v>
+        <v>0.142</v>
       </c>
       <c r="C798">
         <v>43903</v>
@@ -17125,7 +17125,7 @@
         </is>
       </c>
       <c r="B799">
-        <v>20.7</v>
+        <v>0.207</v>
       </c>
       <c r="C799">
         <v>40891</v>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="B800">
-        <v>11.5</v>
+        <v>0.115</v>
       </c>
       <c r="C800">
         <v>47958</v>
@@ -17167,7 +17167,7 @@
         </is>
       </c>
       <c r="B801">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C801">
         <v>56309</v>
@@ -17188,7 +17188,7 @@
         </is>
       </c>
       <c r="B802">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C802">
         <v>49269</v>
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="B803">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C803">
         <v>47651</v>
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="B804">
-        <v>9</v>
+        <v>0.09</v>
       </c>
       <c r="C804">
         <v>50244</v>
@@ -17251,7 +17251,7 @@
         </is>
       </c>
       <c r="B805">
-        <v>15.9</v>
+        <v>0.159</v>
       </c>
       <c r="C805">
         <v>38441</v>
@@ -17272,7 +17272,7 @@
         </is>
       </c>
       <c r="B806">
-        <v>13.4</v>
+        <v>0.134</v>
       </c>
       <c r="C806">
         <v>42752</v>
@@ -17293,7 +17293,7 @@
         </is>
       </c>
       <c r="B807">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C807">
         <v>41907</v>
@@ -17314,7 +17314,7 @@
         </is>
       </c>
       <c r="B808">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C808">
         <v>48039</v>
@@ -17335,7 +17335,7 @@
         </is>
       </c>
       <c r="B809">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C809">
         <v>45825</v>
@@ -17356,7 +17356,7 @@
         </is>
       </c>
       <c r="B810">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C810">
         <v>62676</v>
@@ -17377,7 +17377,7 @@
         </is>
       </c>
       <c r="B811">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C811">
         <v>54320</v>
@@ -17398,7 +17398,7 @@
         </is>
       </c>
       <c r="B812">
-        <v>12.9</v>
+        <v>0.129</v>
       </c>
       <c r="C812">
         <v>42709</v>
@@ -17419,7 +17419,7 @@
         </is>
       </c>
       <c r="B813">
-        <v>11.7</v>
+        <v>0.117</v>
       </c>
       <c r="C813">
         <v>50463</v>
@@ -17440,7 +17440,7 @@
         </is>
       </c>
       <c r="B814">
-        <v>13.5</v>
+        <v>0.135</v>
       </c>
       <c r="C814">
         <v>42279</v>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="B815">
-        <v>10.4</v>
+        <v>0.104</v>
       </c>
       <c r="C815">
         <v>51603</v>
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="B816">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C816">
         <v>45882</v>
@@ -17503,7 +17503,7 @@
         </is>
       </c>
       <c r="B817">
-        <v>14.6</v>
+        <v>0.146</v>
       </c>
       <c r="C817">
         <v>43931</v>
@@ -17524,7 +17524,7 @@
         </is>
       </c>
       <c r="B818">
-        <v>16.4</v>
+        <v>0.164</v>
       </c>
       <c r="C818">
         <v>41304</v>
@@ -17545,7 +17545,7 @@
         </is>
       </c>
       <c r="B819">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C819">
         <v>52700</v>
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="B820">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C820">
         <v>53781</v>
@@ -17587,7 +17587,7 @@
         </is>
       </c>
       <c r="B821">
-        <v>15.4</v>
+        <v>0.154</v>
       </c>
       <c r="C821">
         <v>40950</v>
@@ -17608,7 +17608,7 @@
         </is>
       </c>
       <c r="B822">
-        <v>9.199999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="C822">
         <v>48403</v>
@@ -17629,7 +17629,7 @@
         </is>
       </c>
       <c r="B823">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C823">
         <v>41784</v>
@@ -17650,7 +17650,7 @@
         </is>
       </c>
       <c r="B824">
-        <v>16.3</v>
+        <v>0.163</v>
       </c>
       <c r="C824">
         <v>42209</v>
@@ -17671,7 +17671,7 @@
         </is>
       </c>
       <c r="B825">
-        <v>18.2</v>
+        <v>0.182</v>
       </c>
       <c r="C825">
         <v>45330</v>
@@ -17692,7 +17692,7 @@
         </is>
       </c>
       <c r="B826">
-        <v>8.699999999999999</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="C826">
         <v>54089</v>
@@ -17713,7 +17713,7 @@
         </is>
       </c>
       <c r="B827">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C827">
         <v>42272</v>
@@ -17734,7 +17734,7 @@
         </is>
       </c>
       <c r="B828">
-        <v>16.9</v>
+        <v>0.169</v>
       </c>
       <c r="C828">
         <v>41731</v>
@@ -17755,7 +17755,7 @@
         </is>
       </c>
       <c r="B829">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C829">
         <v>42707</v>
@@ -17776,7 +17776,7 @@
         </is>
       </c>
       <c r="B830">
-        <v>19.7</v>
+        <v>0.197</v>
       </c>
       <c r="C830">
         <v>39250</v>
@@ -17797,7 +17797,7 @@
         </is>
       </c>
       <c r="B831">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C831">
         <v>46192</v>
@@ -17818,7 +17818,7 @@
         </is>
       </c>
       <c r="B832">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C832">
         <v>52888</v>
@@ -17839,7 +17839,7 @@
         </is>
       </c>
       <c r="B833">
-        <v>7.7</v>
+        <v>0.077</v>
       </c>
       <c r="C833">
         <v>55960</v>
@@ -17860,7 +17860,7 @@
         </is>
       </c>
       <c r="B834">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C834">
         <v>42017</v>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="B835">
-        <v>17.2</v>
+        <v>0.172</v>
       </c>
       <c r="C835">
         <v>40783</v>
@@ -17902,7 +17902,7 @@
         </is>
       </c>
       <c r="B836">
-        <v>8.6</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="C836">
         <v>51730</v>
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="B837">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C837">
         <v>45114</v>
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="B838">
-        <v>7.5</v>
+        <v>0.075</v>
       </c>
       <c r="C838">
         <v>49996</v>
@@ -17965,7 +17965,7 @@
         </is>
       </c>
       <c r="B839">
-        <v>14.4</v>
+        <v>0.144</v>
       </c>
       <c r="C839">
         <v>45427</v>
@@ -17986,7 +17986,7 @@
         </is>
       </c>
       <c r="B840">
-        <v>15.8</v>
+        <v>0.158</v>
       </c>
       <c r="C840">
         <v>42994</v>
@@ -18007,7 +18007,7 @@
         </is>
       </c>
       <c r="B841">
-        <v>14.6</v>
+        <v>0.146</v>
       </c>
       <c r="C841">
         <v>47284</v>
@@ -18028,7 +18028,7 @@
         </is>
       </c>
       <c r="B842">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C842">
         <v>49888</v>
@@ -18049,7 +18049,7 @@
         </is>
       </c>
       <c r="B843">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C843">
         <v>42994</v>
@@ -18070,7 +18070,7 @@
         </is>
       </c>
       <c r="B844">
-        <v>14.1</v>
+        <v>0.141</v>
       </c>
       <c r="C844">
         <v>38371</v>
@@ -18091,7 +18091,7 @@
         </is>
       </c>
       <c r="B845">
-        <v>7.9</v>
+        <v>0.079</v>
       </c>
       <c r="C845">
         <v>66166</v>
@@ -18112,7 +18112,7 @@
         </is>
       </c>
       <c r="B846">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C846">
         <v>48388</v>
@@ -18133,7 +18133,7 @@
         </is>
       </c>
       <c r="B847">
-        <v>9.9</v>
+        <v>0.099</v>
       </c>
       <c r="C847">
         <v>48054</v>
@@ -18154,7 +18154,7 @@
         </is>
       </c>
       <c r="B848">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C848">
         <v>43079</v>
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="B849">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C849">
         <v>48284</v>
@@ -18196,7 +18196,7 @@
         </is>
       </c>
       <c r="B850">
-        <v>14</v>
+        <v>0.14</v>
       </c>
       <c r="C850">
         <v>42667</v>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="B851">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C851">
         <v>46315</v>
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="B852">
-        <v>19</v>
+        <v>0.19</v>
       </c>
       <c r="C852">
         <v>36811</v>
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="B853">
-        <v>15.6</v>
+        <v>0.156</v>
       </c>
       <c r="C853">
         <v>41675</v>
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="B854">
-        <v>8.9</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="C854">
         <v>55168</v>
@@ -18301,7 +18301,7 @@
         </is>
       </c>
       <c r="B855">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C855">
         <v>45042</v>
@@ -18322,7 +18322,7 @@
         </is>
       </c>
       <c r="B856">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C856">
         <v>44702</v>
@@ -18343,7 +18343,7 @@
         </is>
       </c>
       <c r="B857">
-        <v>20.7</v>
+        <v>0.207</v>
       </c>
       <c r="C857">
         <v>35935</v>
@@ -18364,7 +18364,7 @@
         </is>
       </c>
       <c r="B858">
-        <v>7.2</v>
+        <v>0.07200000000000001</v>
       </c>
       <c r="C858">
         <v>54687</v>
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="B859">
-        <v>14.4</v>
+        <v>0.144</v>
       </c>
       <c r="C859">
         <v>43531</v>
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="B860">
-        <v>17.8</v>
+        <v>0.178</v>
       </c>
       <c r="C860">
         <v>35343</v>
@@ -18427,7 +18427,7 @@
         </is>
       </c>
       <c r="B861">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C861">
         <v>51812</v>
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="B862">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="C862">
         <v>43678</v>
@@ -18469,7 +18469,7 @@
         </is>
       </c>
       <c r="B863">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C863">
         <v>49117</v>
@@ -18490,7 +18490,7 @@
         </is>
       </c>
       <c r="B864">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C864">
         <v>39535</v>
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="B865">
-        <v>11.4</v>
+        <v>0.114</v>
       </c>
       <c r="C865">
         <v>47446</v>
@@ -18532,7 +18532,7 @@
         </is>
       </c>
       <c r="B866">
-        <v>18.1</v>
+        <v>0.181</v>
       </c>
       <c r="C866">
         <v>38629</v>
@@ -18553,7 +18553,7 @@
         </is>
       </c>
       <c r="B867">
-        <v>16.6</v>
+        <v>0.166</v>
       </c>
       <c r="C867">
         <v>41394</v>
@@ -18574,7 +18574,7 @@
         </is>
       </c>
       <c r="B868">
-        <v>5.6</v>
+        <v>0.05599999999999999</v>
       </c>
       <c r="C868">
         <v>76878</v>
@@ -18595,7 +18595,7 @@
         </is>
       </c>
       <c r="B869">
-        <v>6.5</v>
+        <v>0.065</v>
       </c>
       <c r="C869">
         <v>59652</v>
@@ -18616,7 +18616,7 @@
         </is>
       </c>
       <c r="B870">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C870">
         <v>48028</v>
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="B871">
-        <v>5.1</v>
+        <v>0.051</v>
       </c>
       <c r="C871">
         <v>67011</v>
@@ -18658,7 +18658,7 @@
         </is>
       </c>
       <c r="B872">
-        <v>15</v>
+        <v>0.15</v>
       </c>
       <c r="C872">
         <v>39989</v>
@@ -18679,7 +18679,7 @@
         </is>
       </c>
       <c r="B873">
-        <v>15.1</v>
+        <v>0.151</v>
       </c>
       <c r="C873">
         <v>47108</v>
@@ -18700,7 +18700,7 @@
         </is>
       </c>
       <c r="B874">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C874">
         <v>44820</v>
@@ -18721,7 +18721,7 @@
         </is>
       </c>
       <c r="B875">
-        <v>13.3</v>
+        <v>0.133</v>
       </c>
       <c r="C875">
         <v>41861</v>
@@ -18742,7 +18742,7 @@
         </is>
       </c>
       <c r="B876">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C876">
         <v>53325</v>
@@ -18763,7 +18763,7 @@
         </is>
       </c>
       <c r="B877">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="C877">
         <v>38453</v>
@@ -18784,7 +18784,7 @@
         </is>
       </c>
       <c r="B878">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C878">
         <v>42204</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="B879">
-        <v>15.8</v>
+        <v>0.158</v>
       </c>
       <c r="C879">
         <v>41588</v>
@@ -18826,7 +18826,7 @@
         </is>
       </c>
       <c r="B880">
-        <v>9.699999999999999</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="C880">
         <v>57634</v>
@@ -18847,7 +18847,7 @@
         </is>
       </c>
       <c r="B881">
-        <v>17.8</v>
+        <v>0.178</v>
       </c>
       <c r="C881">
         <v>37805</v>
@@ -18868,7 +18868,7 @@
         </is>
       </c>
       <c r="B882">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C882">
         <v>47152</v>
@@ -18889,7 +18889,7 @@
         </is>
       </c>
       <c r="B883">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C883">
         <v>45578</v>
@@ -18910,7 +18910,7 @@
         </is>
       </c>
       <c r="B884">
-        <v>16.4</v>
+        <v>0.164</v>
       </c>
       <c r="C884">
         <v>47054</v>
@@ -18931,7 +18931,7 @@
         </is>
       </c>
       <c r="B885">
-        <v>14.5</v>
+        <v>0.145</v>
       </c>
       <c r="C885">
         <v>46022</v>
@@ -18952,7 +18952,7 @@
         </is>
       </c>
       <c r="B886">
-        <v>15.4</v>
+        <v>0.154</v>
       </c>
       <c r="C886">
         <v>39398</v>
@@ -18973,7 +18973,7 @@
         </is>
       </c>
       <c r="B887">
-        <v>14.7</v>
+        <v>0.147</v>
       </c>
       <c r="C887">
         <v>41774</v>
@@ -18994,7 +18994,7 @@
         </is>
       </c>
       <c r="B888">
-        <v>19.7</v>
+        <v>0.197</v>
       </c>
       <c r="C888">
         <v>41201</v>
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="B889">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C889">
         <v>46767</v>
@@ -19036,7 +19036,7 @@
         </is>
       </c>
       <c r="B890">
-        <v>13.5</v>
+        <v>0.135</v>
       </c>
       <c r="C890">
         <v>42825</v>
@@ -19057,7 +19057,7 @@
         </is>
       </c>
       <c r="B891">
-        <v>17</v>
+        <v>0.17</v>
       </c>
       <c r="C891">
         <v>39392</v>
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="B892">
-        <v>21.9</v>
+        <v>0.219</v>
       </c>
       <c r="C892">
         <v>36061</v>
@@ -19099,7 +19099,7 @@
         </is>
       </c>
       <c r="B893">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C893">
         <v>47134</v>
@@ -19120,7 +19120,7 @@
         </is>
       </c>
       <c r="B894">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C894">
         <v>55411</v>
@@ -19141,7 +19141,7 @@
         </is>
       </c>
       <c r="B895">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C895">
         <v>47764</v>
@@ -19162,7 +19162,7 @@
         </is>
       </c>
       <c r="B896">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C896">
         <v>43350</v>
@@ -19183,7 +19183,7 @@
         </is>
       </c>
       <c r="B897">
-        <v>10.2</v>
+        <v>0.102</v>
       </c>
       <c r="C897">
         <v>49541</v>
@@ -19204,7 +19204,7 @@
         </is>
       </c>
       <c r="B898">
-        <v>16.9</v>
+        <v>0.169</v>
       </c>
       <c r="C898">
         <v>36620</v>
@@ -19225,7 +19225,7 @@
         </is>
       </c>
       <c r="B899">
-        <v>14.3</v>
+        <v>0.143</v>
       </c>
       <c r="C899">
         <v>41422</v>
@@ -19246,7 +19246,7 @@
         </is>
       </c>
       <c r="B900">
-        <v>15.7</v>
+        <v>0.157</v>
       </c>
       <c r="C900">
         <v>41011</v>
@@ -19267,7 +19267,7 @@
         </is>
       </c>
       <c r="B901">
-        <v>12</v>
+        <v>0.12</v>
       </c>
       <c r="C901">
         <v>44652</v>
@@ -19288,7 +19288,7 @@
         </is>
       </c>
       <c r="B902">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C902">
         <v>40452</v>
@@ -19309,7 +19309,7 @@
         </is>
       </c>
       <c r="B903">
-        <v>7.6</v>
+        <v>0.076</v>
       </c>
       <c r="C903">
         <v>60718</v>
@@ -19330,7 +19330,7 @@
         </is>
       </c>
       <c r="B904">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C904">
         <v>55517</v>
@@ -19351,7 +19351,7 @@
         </is>
       </c>
       <c r="B905">
-        <v>13.1</v>
+        <v>0.131</v>
       </c>
       <c r="C905">
         <v>44483</v>
@@ -19372,7 +19372,7 @@
         </is>
       </c>
       <c r="B906">
-        <v>13.1</v>
+        <v>0.131</v>
       </c>
       <c r="C906">
         <v>47394</v>
@@ -19393,7 +19393,7 @@
         </is>
       </c>
       <c r="B907">
-        <v>17.5</v>
+        <v>0.175</v>
       </c>
       <c r="C907">
         <v>37021</v>
@@ -19414,7 +19414,7 @@
         </is>
       </c>
       <c r="B908">
-        <v>11.8</v>
+        <v>0.118</v>
       </c>
       <c r="C908">
         <v>44179</v>
@@ -19435,7 +19435,7 @@
         </is>
       </c>
       <c r="B909">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C909">
         <v>43716</v>
@@ -19456,7 +19456,7 @@
         </is>
       </c>
       <c r="B910">
-        <v>16.4</v>
+        <v>0.164</v>
       </c>
       <c r="C910">
         <v>43544</v>
@@ -19477,7 +19477,7 @@
         </is>
       </c>
       <c r="B911">
-        <v>16.6</v>
+        <v>0.166</v>
       </c>
       <c r="C911">
         <v>38812</v>
@@ -19498,7 +19498,7 @@
         </is>
       </c>
       <c r="B912">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C912">
         <v>50611</v>
@@ -19519,7 +19519,7 @@
         </is>
       </c>
       <c r="B913">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C913">
         <v>49006</v>
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="B914">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C914">
         <v>40369</v>
@@ -19561,7 +19561,7 @@
         </is>
       </c>
       <c r="B915">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C915">
         <v>45879</v>
@@ -19582,7 +19582,7 @@
         </is>
       </c>
       <c r="B916">
-        <v>17.1</v>
+        <v>0.171</v>
       </c>
       <c r="C916">
         <v>39091</v>
@@ -19603,7 +19603,7 @@
         </is>
       </c>
       <c r="B917">
-        <v>17.2</v>
+        <v>0.172</v>
       </c>
       <c r="C917">
         <v>41837</v>
@@ -19624,7 +19624,7 @@
         </is>
       </c>
       <c r="B918">
-        <v>20.9</v>
+        <v>0.209</v>
       </c>
       <c r="C918">
         <v>41917</v>
@@ -19645,7 +19645,7 @@
         </is>
       </c>
       <c r="B919">
-        <v>9.1</v>
+        <v>0.091</v>
       </c>
       <c r="C919">
         <v>52423</v>
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="B920">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C920">
         <v>43630</v>
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="B921">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C921">
         <v>42404</v>
@@ -19708,7 +19708,7 @@
         </is>
       </c>
       <c r="B922">
-        <v>15.4</v>
+        <v>0.154</v>
       </c>
       <c r="C922">
         <v>40164</v>
@@ -19729,7 +19729,7 @@
         </is>
       </c>
       <c r="B923">
-        <v>20.9</v>
+        <v>0.209</v>
       </c>
       <c r="C923">
         <v>37876</v>
@@ -19750,7 +19750,7 @@
         </is>
       </c>
       <c r="B924">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C924">
         <v>42076</v>
@@ -19771,7 +19771,7 @@
         </is>
       </c>
       <c r="B925">
-        <v>8.800000000000001</v>
+        <v>0.08800000000000001</v>
       </c>
       <c r="C925">
         <v>50841</v>
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="B926">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C926">
         <v>58436</v>
@@ -19813,7 +19813,7 @@
         </is>
       </c>
       <c r="B927">
-        <v>15.5</v>
+        <v>0.155</v>
       </c>
       <c r="C927">
         <v>40419</v>
@@ -19834,7 +19834,7 @@
         </is>
       </c>
       <c r="B928">
-        <v>19.9</v>
+        <v>0.199</v>
       </c>
       <c r="C928">
         <v>38909</v>
@@ -19855,7 +19855,7 @@
         </is>
       </c>
       <c r="B929">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C929">
         <v>48000</v>
@@ -19876,7 +19876,7 @@
         </is>
       </c>
       <c r="B930">
-        <v>10.8</v>
+        <v>0.108</v>
       </c>
       <c r="C930">
         <v>46495</v>
@@ -19897,7 +19897,7 @@
         </is>
       </c>
       <c r="B931">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C931">
         <v>48451</v>
@@ -19918,7 +19918,7 @@
         </is>
       </c>
       <c r="B932">
-        <v>15.3</v>
+        <v>0.153</v>
       </c>
       <c r="C932">
         <v>44616</v>
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="B933">
-        <v>16.8</v>
+        <v>0.168</v>
       </c>
       <c r="C933">
         <v>43121</v>
@@ -19960,7 +19960,7 @@
         </is>
       </c>
       <c r="B934">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C934">
         <v>47014</v>
@@ -19981,7 +19981,7 @@
         </is>
       </c>
       <c r="B935">
-        <v>12.8</v>
+        <v>0.128</v>
       </c>
       <c r="C935">
         <v>49045</v>
@@ -20002,7 +20002,7 @@
         </is>
       </c>
       <c r="B936">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C936">
         <v>47520</v>
@@ -20023,7 +20023,7 @@
         </is>
       </c>
       <c r="B937">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="C937">
         <v>38637</v>
@@ -20044,7 +20044,7 @@
         </is>
       </c>
       <c r="B938">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="C938">
         <v>66023</v>
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="B939">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C939">
         <v>46770</v>
@@ -20086,7 +20086,7 @@
         </is>
       </c>
       <c r="B940">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C940">
         <v>49966</v>
@@ -20107,7 +20107,7 @@
         </is>
       </c>
       <c r="B941">
-        <v>16.7</v>
+        <v>0.167</v>
       </c>
       <c r="C941">
         <v>38859</v>
@@ -20128,7 +20128,7 @@
         </is>
       </c>
       <c r="B942">
-        <v>12.5</v>
+        <v>0.125</v>
       </c>
       <c r="C942">
         <v>44775</v>
@@ -20149,7 +20149,7 @@
         </is>
       </c>
       <c r="B943">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C943">
         <v>42233</v>
@@ -20170,7 +20170,7 @@
         </is>
       </c>
       <c r="B944">
-        <v>12.8</v>
+        <v>0.128</v>
       </c>
       <c r="C944">
         <v>47229</v>
@@ -20191,7 +20191,7 @@
         </is>
       </c>
       <c r="B945">
-        <v>17</v>
+        <v>0.17</v>
       </c>
       <c r="C945">
         <v>39358</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="B946">
-        <v>14.7</v>
+        <v>0.147</v>
       </c>
       <c r="C946">
         <v>42318</v>
@@ -20233,7 +20233,7 @@
         </is>
       </c>
       <c r="B947">
-        <v>10.1</v>
+        <v>0.101</v>
       </c>
       <c r="C947">
         <v>55817</v>
@@ -20254,7 +20254,7 @@
         </is>
       </c>
       <c r="B948">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C948">
         <v>49551</v>
@@ -20275,7 +20275,7 @@
         </is>
       </c>
       <c r="B949">
-        <v>10.6</v>
+        <v>0.106</v>
       </c>
       <c r="C949">
         <v>46781</v>
@@ -20296,7 +20296,7 @@
         </is>
       </c>
       <c r="B950">
-        <v>24.2</v>
+        <v>0.242</v>
       </c>
       <c r="C950">
         <v>36362</v>
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="B951">
-        <v>8.4</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C951">
         <v>51885</v>
@@ -20338,7 +20338,7 @@
         </is>
       </c>
       <c r="B952">
-        <v>17.2</v>
+        <v>0.172</v>
       </c>
       <c r="C952">
         <v>42168</v>
@@ -20359,7 +20359,7 @@
         </is>
       </c>
       <c r="B953">
-        <v>17</v>
+        <v>0.17</v>
       </c>
       <c r="C953">
         <v>36734</v>
@@ -20380,7 +20380,7 @@
         </is>
       </c>
       <c r="B954">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C954">
         <v>49117</v>
@@ -20401,7 +20401,7 @@
         </is>
       </c>
       <c r="B955">
-        <v>12.4</v>
+        <v>0.124</v>
       </c>
       <c r="C955">
         <v>43947</v>
@@ -20422,7 +20422,7 @@
         </is>
       </c>
       <c r="B956">
-        <v>12.3</v>
+        <v>0.123</v>
       </c>
       <c r="C956">
         <v>48938</v>
@@ -20443,7 +20443,7 @@
         </is>
       </c>
       <c r="B957">
-        <v>13.8</v>
+        <v>0.138</v>
       </c>
       <c r="C957">
         <v>40856</v>
@@ -20464,7 +20464,7 @@
         </is>
       </c>
       <c r="B958">
-        <v>12.1</v>
+        <v>0.121</v>
       </c>
       <c r="C958">
         <v>45383</v>
@@ -20485,7 +20485,7 @@
         </is>
       </c>
       <c r="B959">
-        <v>19.8</v>
+        <v>0.198</v>
       </c>
       <c r="C959">
         <v>35976</v>
@@ -20506,7 +20506,7 @@
         </is>
       </c>
       <c r="B960">
-        <v>14</v>
+        <v>0.14</v>
       </c>
       <c r="C960">
         <v>41504</v>
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="B961">
-        <v>4.9</v>
+        <v>0.049</v>
       </c>
       <c r="C961">
         <v>82054</v>
@@ -20548,7 +20548,7 @@
         </is>
       </c>
       <c r="B962">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C962">
         <v>62195</v>
@@ -20569,7 +20569,7 @@
         </is>
       </c>
       <c r="B963">
-        <v>11</v>
+        <v>0.11</v>
       </c>
       <c r="C963">
         <v>48775</v>
@@ -20590,7 +20590,7 @@
         </is>
       </c>
       <c r="B964">
-        <v>6.4</v>
+        <v>0.064</v>
       </c>
       <c r="C964">
         <v>66080</v>
@@ -20611,7 +20611,7 @@
         </is>
       </c>
       <c r="B965">
-        <v>16.2</v>
+        <v>0.162</v>
       </c>
       <c r="C965">
         <v>40732</v>
@@ -20632,7 +20632,7 @@
         </is>
       </c>
       <c r="B966">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="C966">
         <v>41786</v>
@@ -20653,7 +20653,7 @@
         </is>
       </c>
       <c r="B967">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C967">
         <v>46530</v>
@@ -20674,7 +20674,7 @@
         </is>
       </c>
       <c r="B968">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C968">
         <v>46562</v>
@@ -20695,7 +20695,7 @@
         </is>
       </c>
       <c r="B969">
-        <v>9.5</v>
+        <v>0.095</v>
       </c>
       <c r="C969">
         <v>55267</v>
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="B970">
-        <v>15.6</v>
+        <v>0.156</v>
       </c>
       <c r="C970">
         <v>38117</v>
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="B971">
-        <v>15.9</v>
+        <v>0.159</v>
       </c>
       <c r="C971">
         <v>41654</v>
@@ -20758,7 +20758,7 @@
         </is>
       </c>
       <c r="B972">
-        <v>14.2</v>
+        <v>0.142</v>
       </c>
       <c r="C972">
         <v>41869</v>
@@ -20779,7 +20779,7 @@
         </is>
       </c>
       <c r="B973">
-        <v>10.5</v>
+        <v>0.105</v>
       </c>
       <c r="C973">
         <v>58695</v>
@@ -20800,7 +20800,7 @@
         </is>
       </c>
       <c r="B974">
-        <v>17.6</v>
+        <v>0.176</v>
       </c>
       <c r="C974">
         <v>39123</v>
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="B975">
-        <v>13.4</v>
+        <v>0.134</v>
       </c>
       <c r="C975">
         <v>47811</v>
@@ -20842,7 +20842,7 @@
         </is>
       </c>
       <c r="B976">
-        <v>16.1</v>
+        <v>0.161</v>
       </c>
       <c r="C976">
         <v>44151</v>
@@ -20863,7 +20863,7 @@
         </is>
       </c>
       <c r="B977">
-        <v>17.7</v>
+        <v>0.177</v>
       </c>
       <c r="C977">
         <v>45252</v>
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="B978">
-        <v>16.2</v>
+        <v>0.162</v>
       </c>
       <c r="C978">
         <v>44039</v>
@@ -20905,7 +20905,7 @@
         </is>
       </c>
       <c r="B979">
-        <v>15.2</v>
+        <v>0.152</v>
       </c>
       <c r="C979">
         <v>41305</v>
@@ -20926,7 +20926,7 @@
         </is>
       </c>
       <c r="B980">
-        <v>18</v>
+        <v>0.18</v>
       </c>
       <c r="C980">
         <v>39449</v>
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="B981">
-        <v>20.8</v>
+        <v>0.208</v>
       </c>
       <c r="C981">
         <v>39393</v>
@@ -20968,7 +20968,7 @@
         </is>
       </c>
       <c r="B982">
-        <v>12.7</v>
+        <v>0.127</v>
       </c>
       <c r="C982">
         <v>43283</v>
@@ -20989,7 +20989,7 @@
         </is>
       </c>
       <c r="B983">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C983">
         <v>43854</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="B984">
-        <v>17</v>
+        <v>0.17</v>
       </c>
       <c r="C984">
         <v>40466</v>
@@ -21031,7 +21031,7 @@
         </is>
       </c>
       <c r="B985">
-        <v>24.3</v>
+        <v>0.243</v>
       </c>
       <c r="C985">
         <v>38348</v>
@@ -21052,7 +21052,7 @@
         </is>
       </c>
       <c r="B986">
-        <v>15.3</v>
+        <v>0.153</v>
       </c>
       <c r="C986">
         <v>41853</v>
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="B987">
-        <v>11.9</v>
+        <v>0.119</v>
       </c>
       <c r="C987">
         <v>53738</v>
@@ -21094,7 +21094,7 @@
         </is>
       </c>
       <c r="B988">
-        <v>11.1</v>
+        <v>0.111</v>
       </c>
       <c r="C988">
         <v>48043</v>
@@ -21115,7 +21115,7 @@
         </is>
       </c>
       <c r="B989">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C989">
         <v>45269</v>
@@ -21136,7 +21136,7 @@
         </is>
       </c>
       <c r="B990">
-        <v>10</v>
+        <v>0.1</v>
       </c>
       <c r="C990">
         <v>47937</v>
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="B991">
-        <v>17.5</v>
+        <v>0.175</v>
       </c>
       <c r="C991">
         <v>35999</v>
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="B992">
-        <v>14.1</v>
+        <v>0.141</v>
       </c>
       <c r="C992">
         <v>42658</v>
@@ -21199,7 +21199,7 @@
         </is>
       </c>
       <c r="B993">
-        <v>16.6</v>
+        <v>0.166</v>
       </c>
       <c r="C993">
         <v>42749</v>
@@ -21220,7 +21220,7 @@
         </is>
       </c>
       <c r="B994">
-        <v>13</v>
+        <v>0.13</v>
       </c>
       <c r="C994">
         <v>41446</v>
@@ -21241,7 +21241,7 @@
         </is>
       </c>
       <c r="B995">
-        <v>14.7</v>
+        <v>0.147</v>
       </c>
       <c r="C995">
         <v>39684</v>
@@ -21262,7 +21262,7 @@
         </is>
       </c>
       <c r="B996">
-        <v>10.9</v>
+        <v>0.109</v>
       </c>
       <c r="C996">
         <v>56648</v>
@@ -21283,7 +21283,7 @@
         </is>
       </c>
       <c r="B997">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C997">
         <v>56159</v>
@@ -21304,7 +21304,7 @@
         </is>
       </c>
       <c r="B998">
-        <v>14.2</v>
+        <v>0.142</v>
       </c>
       <c r="C998">
         <v>41794</v>
@@ -21325,7 +21325,7 @@
         </is>
       </c>
       <c r="B999">
-        <v>13.9</v>
+        <v>0.139</v>
       </c>
       <c r="C999">
         <v>44437</v>
@@ -21346,7 +21346,7 @@
         </is>
       </c>
       <c r="B1000">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="C1000">
         <v>40806</v>
@@ -21367,7 +21367,7 @@
         </is>
       </c>
       <c r="B1001">
-        <v>10.7</v>
+        <v>0.107</v>
       </c>
       <c r="C1001">
         <v>45951</v>
@@ -21388,7 +21388,7 @@
         </is>
       </c>
       <c r="B1002">
-        <v>13.2</v>
+        <v>0.132</v>
       </c>
       <c r="C1002">
         <v>45464</v>
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="B1003">
-        <v>15.9</v>
+        <v>0.159</v>
       </c>
       <c r="C1003">
         <v>42316</v>
@@ -21430,7 +21430,7 @@
         </is>
       </c>
       <c r="B1004">
-        <v>18.8</v>
+        <v>0.188</v>
       </c>
       <c r="C1004">
         <v>39134</v>
@@ -21451,7 +21451,7 @@
         </is>
       </c>
       <c r="B1005">
-        <v>12.8</v>
+        <v>0.128</v>
       </c>
       <c r="C1005">
         <v>46619</v>
@@ -21472,7 +21472,7 @@
         </is>
       </c>
       <c r="B1006">
-        <v>11.3</v>
+        <v>0.113</v>
       </c>
       <c r="C1006">
         <v>47726</v>
@@ -21493,7 +21493,7 @@
         </is>
       </c>
       <c r="B1007">
-        <v>18.2</v>
+        <v>0.182</v>
       </c>
       <c r="C1007">
         <v>38317</v>
@@ -21514,7 +21514,7 @@
         </is>
       </c>
       <c r="B1008">
-        <v>12.8</v>
+        <v>0.128</v>
       </c>
       <c r="C1008">
         <v>45431</v>
@@ -21535,7 +21535,7 @@
         </is>
       </c>
       <c r="B1009">
-        <v>14.7</v>
+        <v>0.147</v>
       </c>
       <c r="C1009">
         <v>42481</v>
@@ -21556,7 +21556,7 @@
         </is>
       </c>
       <c r="B1010">
-        <v>16.3</v>
+        <v>0.163</v>
       </c>
       <c r="C1010">
         <v>42268</v>
@@ -21577,7 +21577,7 @@
         </is>
       </c>
       <c r="B1011">
-        <v>20.9</v>
+        <v>0.209</v>
       </c>
       <c r="C1011">
         <v>41722</v>
@@ -21598,7 +21598,7 @@
         </is>
       </c>
       <c r="B1012">
-        <v>8.5</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C1012">
         <v>54171</v>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="B1013">
-        <v>12.6</v>
+        <v>0.126</v>
       </c>
       <c r="C1013">
         <v>44337</v>
@@ -21640,7 +21640,7 @@
         </is>
       </c>
       <c r="B1014">
-        <v>16.9</v>
+        <v>0.169</v>
       </c>
       <c r="C1014">
         <v>41024</v>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="B1015">
-        <v>13.6</v>
+        <v>0.136</v>
       </c>
       <c r="C1015">
         <v>42613</v>
@@ -21682,7 +21682,7 @@
         </is>
       </c>
       <c r="B1016">
-        <v>19.1</v>
+        <v>0.191</v>
       </c>
       <c r="C1016">
         <v>39089</v>
@@ -21703,7 +21703,7 @@
         </is>
       </c>
       <c r="B1017">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C1017">
         <v>42990</v>
@@ -21724,7 +21724,7 @@
         </is>
       </c>
       <c r="B1018">
-        <v>9.800000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="C1018">
         <v>50349</v>
@@ -21745,7 +21745,7 @@
         </is>
       </c>
       <c r="B1019">
-        <v>7.3</v>
+        <v>0.073</v>
       </c>
       <c r="C1019">
         <v>59195</v>
@@ -21766,7 +21766,7 @@
         </is>
       </c>
       <c r="B1020">
-        <v>15.9</v>
+        <v>0.159</v>
       </c>
       <c r="C1020">
         <v>39945</v>
@@ -21787,7 +21787,7 @@
         </is>
       </c>
       <c r="B1021">
-        <v>20.3</v>
+        <v>0.203</v>
       </c>
       <c r="C1021">
         <v>36424</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="B1022">
-        <v>9.6</v>
+        <v>0.096</v>
       </c>
       <c r="C1022">
         <v>45492</v>
@@ -21829,7 +21829,7 @@
         </is>
       </c>
       <c r="B1023">
-        <v>12.2</v>
+        <v>0.122</v>
       </c>
       <c r="C1023">
         <v>43487</v>
@@ -21850,7 +21850,7 @@
         </is>
       </c>
       <c r="B1024">
-        <v>9.300000000000001</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="C1024">
         <v>49989</v>
